--- a/data_extactor/batch_10_fa/batch_0024_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0024_fa.xlsx
@@ -493,42 +493,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Climate Change Policy Analysts (تحلیل‌گران سیاست تغییرات اقلیمی)</t>
+          <t>تحلیل‌گران سیاست تغییرات اقلیمی (Climate Change Policy Analysts)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Climate Advisor | Climate Analyst | Climate Economist | Climate and Energy Program Associate | Environmental Policy Analyst | Policy Analyst | Policy Associate | Policy Research Associate | Regional Science Advisor</t>
+          <t>مشاور اقلیم | تحلیل‌گر اقلیم | اقتصاددان اقلیم | کارشناس برنامه اقلیم و انرژی | تحلیل‌گر سیاست محیط‌زیستی | تحلیلگر سیاست‌گذاری | کارشناس سیاست‌گذاری | کارشناس پژوهش سیاستی | مشاور علمی منطقه‌ای</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C++ | Community Climate System Model CCSM | ESRI ArcGIS software | Ferret | Formula translation/translator FORTRAN | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Grid analysis and display system GrADS | Interface definition language IDL | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | NCAR Command Language NCL | North American Regional Climate Change Assessment Program NARCCAP data tables | Perl | Python | R | SAS | Sun Microsystems Java | The MathWorks MATLAB | UNIX | Unidata Integrated Data Viewer IDV | Unidata Network common data form NetCDF | نرم‌افزار مرورگر وب</t>
+          <t>C++ | Community Climate System Model CCSM | نرم‌افزار ESRI ArcGIS | Ferret | Formula translation/translator FORTRAN | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Grid analysis and display system GrADS | زبان تعریف رابط IDL | Linux | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | NCAR Command Language NCL | North American Regional Climate Change Assessment Program NARCCAP data tables | Perl | Python | R | SAS | Sun Microsystems Java | The MathWorks MATLAB | UNIX | Unidata Integrated Data Viewer IDV | Unidata Network common data form NetCDF | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Critical Thinking | Active Listening | Writing | Speaking | Active Learning | Monitoring | Mathematics | Learning Strategies</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Law and Government | English Language | Mathematics</t>
+          <t>قانون و دولت | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Written Comprehension | Oral Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Near Vision | Problem Sensitivity | Information Ordering | Speech Recognition | Speech Clarity | Flexibility of Closure | Category Flexibility | Originality | Fluency of Ideas | Mathematical Reasoning | Selective Attention | Number Facility</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | استدلال ریاضی | توجه انتخابی | توانایی عددی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Spend Time Sitting | Freedom to Make Decisions | Contact With Others | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Coordinate or Lead Others in Accomplishing Work Activities</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Atmospheric and Space Scientists | Brownfield Redevelopment Specialists and Site Managers | Chief Sustainability Officers | Conservation Scientists | Economists | Environmental Compliance Inspectors | Environmental Economists | Environmental Engineers | Environmental Restoration Planners | Environmental Science Teachers, Postsecondary | Environmental Scientists and Specialists, Including Health | Financial Risk Specialists | Geoscientists, Except Hydrologists and Geographers | Hydrologic Technicians | Hydrologists | Industrial Ecologists | Political Scientists | Sustainability Specialists | Urban and Regional Planners | Water Resource Specialists</t>
+          <t>دانشمندان علوم جوی و فضایی | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | دانشمندان حفاظت | اقتصاددانان | بازرسان انطباق زیست‌محیطی | اقتصاددانان محیط‌زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | مدرسان علوم محیطی، پس از متوسطه | دانشمندان و متخصصان محیط زیست، شامل بهداشت | متخصصان ریسک مالی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | دانشمندان علوم سیاسی | متخصصان پایداری | برنامه‌ریزان شهری و منطقه‌ای | متخصصان منابع آب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Analyze and distill climate-related research findings to inform legislators, regulatory agencies, or other stakeholders. | Develop, or contribute to the development of, educational or outreach programs on the environment or climate change. | Gather and review climate-related studies from government agencies, research laboratories, and other organizations. | Make legislative recommendations related to climate change or environmental management, based on climate change policies, principles, programs, practices, and processes. | Prepare grant applications to obtain funding for programs related to climate change, environmental management, or sustainability. | Prepare study reports, memoranda, briefs, testimonies, or other written materials to inform government or environmental groups on environmental issues, such as climate change. | Present and defend proposals for climate change research projects. | Present climate-related information at public interest, governmental, or other meetings. | Promote initiatives to mitigate climate change with government or environmental groups. | Propose new or modified policies involving use of traditional and alternative fuels, transportation of goods, and other factors relating to climate and climate change. | Provide analytical support for policy briefs related to renewable energy, energy efficiency, or climate change. | Research policies, practices, or procedures for climate or environmental management. | Review existing policies or legislation to identify environmental impacts. | Write reports or academic papers to communicate findings of climate-related studies.</t>
+          <t>تجزیه و تحلیل و تلخیص یافته‌های پژوهشی مرتبط با اقلیم برای آگاهی‌بخشی به قانون‌گذاران، نهادهای نظارتی یا سایر ذی‌نفعان. | تدوین برنامه‌های آموزشی یا ترویجی در زمینه محیط‌زیست یا تغییر اقلیم، یا مشارکت در تدوین آن‌ها. | گردآوری و بازبینی مطالعات مرتبط با اقلیم از نهادهای دولتی، آزمایشگاه‌های پژوهشی و سایر سازمان‌ها. | ارائه پیشنهادهای قانون‌گذاری مرتبط با تغییر اقلیم یا مدیریت محیط‌زیست، بر پایه سیاست‌ها، اصول، برنامه‌ها، شیوه‌ها و فرایندهای تغییر اقلیم. | تهیه درخواست‌های اعطای اعتبار برای تأمین مالی برنامه‌های مرتبط با تغییر اقلیم، مدیریت محیط‌زیست یا پایداری. | تهیه گزارش‌های مطالعاتی، یادداشت‌ها، خلاصه‌ها، شهادت‌ها یا سایر مواد مکتوب برای آگاهی‌بخشی به نهادهای دولتی یا گروه‌های محیط‌زیستی درباره مسائل محیط‌زیستی، مانند تغییر اقلیم. | ارائه و دفاع از پیشنهادهای پروژه‌های پژوهشی تغییر اقلیم. | ارائه اطلاعات مرتبط با اقلیم در نشست‌های عمومی، دولتی یا سایر نشست‌ها. | ترویج ابتکارهای کاهش تغییر اقلیم نزد نهادهای دولتی یا گروه‌های محیط‌زیستی. | پیشنهاد سیاست‌های جدید یا اصلاح‌شده درباره استفاده از سوخت‌های سنتی و جایگزین، حمل‌ونقل کالا و سایر عوامل مرتبط با اقلیم و تغییر اقلیم. | ارائه پشتیبانی تحلیلی برای خلاصه‌های سیاستی مرتبط با انرژی تجدیدپذیر، بهره‌وری انرژی یا تغییر اقلیم. | پژوهش درباره سیاست‌ها، شیوه‌ها یا رویه‌های مدیریت اقلیم یا محیط‌زیست. | بازبینی سیاست‌ها یا قوانین موجود برای شناسایی پیامدهای محیط‌زیستی آن‌ها. | نگارش گزارش‌ها یا مقالات علمی برای انتقال یافته‌های مطالعات مرتبط با اقلیم.</t>
         </is>
       </c>
     </row>
@@ -550,42 +550,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Environmental Restoration Planners (برنامه‌ریزان احیای محیط‌زیست)</t>
+          <t>برنامه‌ریزان احیای محیط‌زیست (Environmental Restoration Planners)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Coastal and Estuary Specialist | Fisheries Habitat Restoration Specialist | Habitat Restoration Specialist | Marine Habitat Resources Specialist | Restoration Ecologist | Restoration Specialist | Watershed Coordinator</t>
+          <t>کارشناس مناطق ساحلی و مصبی | کارشناس احیای زیستگاه آبزیان | کارشناس احیای زیستگاه | کارشناس منابع زیستگاه دریایی | بوم‌شناس احیا | کارشناس احیا | هماهنگ‌کننده حوضه آبریز</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | ESRI ArcGIS software | ESRI ArcMap | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HEC-RAS | IWR-PLAN | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics CRM | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Word | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Acrobat | نرم‌افزار Adobe Creative Cloud | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | نرم‌افزار ESRI ArcGIS | ESRI ArcMap | نرم‌افزار ایمیل | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | HEC-RAS | IWR-PLAN | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics CRM | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Word | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Critical Thinking | Speaking | Reading Comprehension | Active Listening | Writing | Monitoring | Science | Active Learning | Mathematics | Learning Strategies</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | نظارت | علوم | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Biology | English Language | Geography | Design | Mathematics | Administration and Management | Customer and Personal Service | Law and Government | Engineering and Technology | Computers and Electronics | Building and Construction</t>
+          <t>زیست‌شناسی | زبان انگلیسی | جغرافیا | طراحی | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | مهندسی و فناوری | رایانه و الکترونیک | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Information Ordering | Speech Clarity | Speech Recognition | Near Vision | Mathematical Reasoning | Category Flexibility | Fluency of Ideas | Number Facility | Far Vision | Originality | Visualization | Flexibility of Closure</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توانایی عددی | بینایی دور | اصالت | تجسم | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>E-Mail | Work With or Contribute to a Work Group or Team | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities | In an Enclosed Vehicle or Operate Enclosed Equipment | Indoors, Environmentally Controlled | Written Letters and Memos | Deal With External Customers or the Public in General | Outdoors, Exposed to All Weather Conditions | Spend Time Sitting</t>
+          <t>ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | محیط داخلی، دارای کنترل شرایط محیطی | نامه‌ها و یادداشت‌های کتبی | تعامل با مشتریان خارجی یا عموم مردم | فضای باز، در معرض تمام شرایط آب و هوایی | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Biologists | Brownfield Redevelopment Specialists and Site Managers | Chief Sustainability Officers | Civil Engineers | Climate Change Policy Analysts | Conservation Scientists | Environmental Engineers | Environmental Science and Protection Technicians, Including Health | Environmental Scientists and Specialists, Including Health | Forest and Conservation Technicians | Foresters | Geoscientists, Except Hydrologists and Geographers | Hydrologic Technicians | Hydrologists | Industrial Ecologists | Range Managers | Soil and Plant Scientists | Water Resource Specialists | Water/Wastewater Engineers | Zoologists and Wildlife Biologists</t>
+          <t>زیست‌شناسان | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | مهندسان عمران | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان حفاظت | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تکنسین‌های جنگل و حفاظت | جنگل‌بانان | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | مدیران مراتع | دانشمندان خاک و گیاه | متخصصان منابع آب | مهندسان آب و فاضلاب | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Apply for permits required for the implementation of environmental remediation projects. | Collect and analyze data to determine environmental conditions and restoration needs. | Communicate findings of environmental studies or proposals for environmental remediation to other restoration professionals. | Conduct environmental impact studies to examine the ecological effects of pollutants, disease, human activities, nature, and climate change. | Conduct feasibility and cost-benefit studies for environmental remediation projects. | Conduct site assessments to certify a habitat or to ascertain environmental damage or restoration needs. | Create diagrams to communicate environmental remediation planning, using geographic information systems (GIS), computer-aided design (CAD), or other mapping or diagramming software. | Create environmental models or simulations, using geographic information system (GIS) data and knowledge of particular ecosystems or ecological regions. | Create habitat management or restoration plans, such as native tree restoration and weed control. | Develop and communicate recommendations for landowners to maintain or restore environmental conditions. | Develop environmental management or restoration plans for sites with power transmission lines, natural gas pipelines, fuel refineries, geothermal plants, wind farms, or solar farms. | Develop environmental restoration project schedules and budgets. | Develop natural resource management plans, using knowledge of environmental planning or state and federal environmental regulatory requirements. | Identify environmental mitigation alternatives, ensuring compliance with applicable standards, laws, or regulations. | Identify short- and long-term impacts of environmental remediation activities. | Inspect active remediation sites to ensure compliance with environmental or safety policies, standards, or regulations. | Notify regulatory or permitting agencies of deviations from implemented remediation plans. | Plan environmental restoration projects, using biological databases, environmental strategies, and planning software. | Plan or supervise environmental studies to achieve compliance with environmental regulations in construction, modification, operation, acquisition, or divestiture of facilities such as power plants. | Provide technical direction on environmental planning to energy engineers, biologists, geologists, or other professionals working to develop restoration plans or strategies. | Review existing environmental remediation designs. | Supervise and provide technical guidance, training, or assistance to employees working in the field to restore habitats. | Write grants to obtain funding for restoration projects.</t>
+          <t>درخواست مجوزهای لازم برای اجرای پروژه‌های پاک‌سازی محیط‌زیستی. | گردآوری و تجزیه و تحلیل داده‌ها برای تعیین شرایط محیط‌زیستی و نیازهای احیا. | انتقال یافته‌های مطالعات محیط‌زیستی یا پیشنهادهای پاک‌سازی محیط‌زیستی به سایر متخصصان احیا. | انجام مطالعات ارزیابی اثرات محیط‌زیستی برای بررسی آثار بوم‌شناختی آلاینده‌ها، بیماری، فعالیت‌های انسانی، طبیعت و تغییر اقلیم. | انجام مطالعات امکان‌سنجی و هزینه‌فایده برای پروژه‌های پاک‌سازی محیط‌زیستی. | انجام ارزیابی‌های سایت برای تأیید یک زیستگاه یا تعیین آسیب محیط‌زیستی و نیازهای احیا. | ترسیم نمودار برای انتقال برنامه‌ریزی پاک‌سازی محیط‌زیستی، با استفاده از سامانه اطلاعات جغرافیایی (GIS)، طراحی به کمک رایانه (CAD) یا سایر نرم‌افزارهای نقشه‌کشی و نمودارسازی. | ساخت مدل‌ها یا شبیه‌سازی‌های محیط‌زیستی، با استفاده از داده‌های سامانه اطلاعات جغرافیایی (GIS) و دانش بوم‌سازگان‌ها یا مناطق بوم‌شناختی خاص. | تدوین برنامه‌های مدیریت یا احیای زیستگاه، مانند احیای درختان بومی و کنترل علف‌های هرز. | تدوین و ابلاغ توصیه‌ها به مالکان زمین برای حفظ یا احیای شرایط محیط‌زیستی. | تدوین برنامه‌های مدیریت یا احیای محیط‌زیست برای محل‌های دارای خطوط انتقال برق، خطوط لوله گاز طبیعی، پالایشگاه سوخت، نیروگاه زمین‌گرمایی، مزرعه بادی یا مزرعه خورشیدی. | تدوین زمان‌بندی و بودجه پروژه‌های احیای محیط‌زیست. | تدوین برنامه‌های مدیریت منابع طبیعی، با به‌کارگیری دانش برنامه‌ریزی محیط‌زیستی یا الزامات نظارتی محیط‌زیستی ایالتی و فدرال. | شناسایی گزینه‌های جایگزین برای کاهش اثرات محیط‌زیستی، با اطمینان از رعایت استانداردها، قوانین یا مقررات مربوطه. | شناسایی اثرات کوتاه‌مدت و بلندمدت فعالیت‌های پاک‌سازی محیط‌زیستی. | بازرسی محل‌های فعال پاک‌سازی برای اطمینان از رعایت سیاست‌ها، استانداردها یا مقررات محیط‌زیستی و ایمنی. | اطلاع‌رسانی به نهادهای نظارتی یا صادرکننده مجوز درباره انحراف از برنامه‌های پاک‌سازی اجراشده. | برنامه‌ریزی پروژه‌های احیای محیط‌زیست، با استفاده از پایگاه‌های داده زیستی، راهبردهای محیط‌زیستی و نرم‌افزارهای برنامه‌ریزی. | برنامه‌ریزی یا سرپرستی مطالعات محیط‌زیستی برای دستیابی به انطباق با مقررات محیط‌زیستی در ساخت، اصلاح، بهره‌برداری، تملک یا واگذاری تأسیساتی مانند نیروگاه‌ها. | ارائه راهبری فنی در زمینه برنامه‌ریزی محیط‌زیستی به مهندسان انرژی، زیست‌شناسان، زمین‌شناسان یا سایر متخصصانی که برنامه‌ها یا راهبردهای احیا را تدوین می‌کنند. | بازبینی طرح‌های موجود پاک‌سازی محیط‌زیستی. | سرپرستی و ارائه راهنمایی فنی، آموزش یا کمک به کارکنان میدانی که در احیای زیستگاه‌ها فعالیت می‌کنند. | نگارش درخواست‌های اعطای اعتبار برای تأمین مالی پروژه‌های احیا.</t>
         </is>
       </c>
     </row>
@@ -607,42 +607,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Industrial Ecologists (بوم‌شناسان صنعتی)</t>
+          <t>بوم‌شناسان صنعتی (Industrial Ecologists)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecologist | Environmental Consultant | Environmental Protection Agency Counselor | Research Scientist | Researcher</t>
+          <t>اکولوژیست | مشاور محیط زیست | مشاور سازمان حفاظت محیط‌زیست | دانشمند پژوهشی | پژوهشگر</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Adobe Acrobat | Adobe Illustrator | Adobe Photoshop | Apache Hadoop | Atlassian JIRA | Autodesk AutoCAD | C# | Dassault Systemes CATIA | نرم‌افزار عیب‌یابی | ESRI ArcGIS software | Economic Input-Output Life Cycle Assessment EIO-LCA | نرم‌افزار ایمیل | Git | Linux | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics AX | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Studio | Microsoft Windows | NoSQL | پایگاه‌های داده آنلاین | Oracle Database | Oracle Java | PRe Consultants SimaPro | Production Flow Analysis and Simplification Toolkit PFAST | نرم‌افزار بهره‌وری | Python | نرم‌افزار SAP | SAS | STATISTICA | نرم‌افزار اتوماسیون فروش | نرم‌افزار Salesforce | Splunk Enterprise | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Substance Flow Analysis STAN | The MathWorks MATLAB | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
+          <t>Adobe Acrobat | Adobe Illustrator | Adobe Photoshop | Apache Hadoop | Atlassian JIRA | Autodesk AutoCAD | C# | Dassault Systemes CATIA | نرم‌افزار عیب‌یابی | نرم‌افزار ESRI ArcGIS | Economic Input-Output Life Cycle Assessment EIO-LCA | نرم‌افزار ایمیل | Git | Linux | Microsoft Access | Microsoft Dynamics | Microsoft Dynamics AX | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Studio | Microsoft Windows | NoSQL | پایگاه‌های داده آنلاین | Oracle Database | Oracle Java | PRe Consultants SimaPro | Production Flow Analysis and Simplification Toolkit PFAST | نرم‌افزار بهره‌وری | Python | نرم‌افزار SAP | SAS | STATISTICA | نرم‌افزار اتوماسیون فروش | نرم‌افزار Salesforce | Splunk Enterprise | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Substance Flow Analysis STAN | The MathWorks MATLAB | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Speaking | Writing | Active Listening | Critical Thinking | Science | Active Learning | Mathematics | Monitoring | Learning Strategies</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mathematics | Engineering and Technology | Chemistry | Computers and Electronics | Physics | English Language | Production and Processing | Design | Biology</t>
+          <t>ریاضیات | مهندسی و فناوری | شیمی | رایانه و الکترونیک | فیزیک | زبان انگلیسی | تولید و فرآوری | طراحی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Deductive Reasoning | Inductive Reasoning | Written Expression | Oral Expression | Problem Sensitivity | Oral Comprehension | Written Comprehension | Information Ordering | Near Vision | Speech Clarity | Mathematical Reasoning | Speech Recognition | Category Flexibility | Originality | Fluency of Ideas | Flexibility of Closure | Number Facility | Far Vision</t>
+          <t>استدلال قیاسی | استدلال استقرایی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | استدلال ریاضی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار | توانایی عددی | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>E-Mail | Determine Tasks, Priorities and Goals | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Telephone Conversations | Spend Time Sitting | Importance of Being Exact or Accurate | Work With or Contribute to a Work Group or Team | Contact With Others | Written Letters and Memos</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | مکالمات تلفنی | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Agricultural Engineers | Biofuels/Biodiesel Technology and Product Development Managers | Brownfield Redevelopment Specialists and Site Managers | Chief Sustainability Officers | Climate Change Policy Analysts | Conservation Scientists | Environmental Economists | Environmental Engineering Technologists and Technicians | Environmental Engineers | Environmental Restoration Planners | Environmental Science and Protection Technicians, Including Health | Environmental Scientists and Specialists, Including Health | Geoscientists, Except Hydrologists and Geographers | Hydrologic Technicians | Hydrologists | Range Managers | Soil and Plant Scientists | Sustainability Specialists | Water Resource Specialists | Water/Wastewater Engineers</t>
+          <t>مهندسان کشاورزی | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | مدیران ارشد پایداری | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان حفاظت | اقتصاددانان محیط‌زیست | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | آب‌شناسان | مدیران مراتع | دانشمندان خاک و گیاه | متخصصان پایداری | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Analyze changes designed to improve the environmental performance of complex systems and avoid unintended negative consequences. | Apply new or existing research about natural ecosystems to understand economic and industrial systems in the context of the environment. | Build and maintain databases of information about energy alternatives, pollutants, natural environments, industrial processes, and other information related to ecological change. | Carry out environmental assessments in accordance with applicable standards, regulations, or laws. | Conduct analyses to determine the maximum amount of work that can be accomplished for a given amount of energy in a system, such as industrial production systems and waste treatment systems. | Conduct applied research on the effects of industrial processes on the protection, restoration, inventory, monitoring, or reintroduction of species to the natural environment. | Conduct environmental sustainability assessments, using material flow analysis (MFA) or substance flow analysis (SFA) techniques. | Conduct scientific protection, mitigation, or restoration projects to prevent resource damage, maintain the integrity of critical habitats, and minimize the impact of human activities. | Create complex and dynamic mathematical models of population, community, or ecological systems. | Develop alternative energy investment scenarios to compare economic and environmental costs and benefits. | Develop or test protocols to monitor ecosystem components and ecological processes. | Evaluate the effectiveness of industrial ecology programs, using statistical analysis and applications. | Examine local, regional, or global use and flow of materials or energy in industrial production processes. | Examine societal issues and their relationship with both technical systems and the environment. | Forecast future status or condition of ecosystems, based on changing industrial practices or environmental conditions. | Identify environmental impacts caused by products, systems, or projects. | Identify or compare the component parts or relationships between the parts of industrial, social, and natural systems. | Identify or develop strategies or methods to minimize the environmental impact of industrial production processes. | Identify sustainable alternatives to industrial or waste-management practices. | Investigate accidents affecting the environment to assess ecological impact. | Investigate the adaptability of various animal and plant species to changed environmental conditions. | Investigate the impact of changed land management or land use practices on ecosystems. | Monitor the environmental impact of development activities, pollution, or land degradation. | Perform analyses to determine how human behavior can affect, and be affected by, changes in the environment. | Perform environmentally extended input-output (EE I-O) analyses. | Plan or conduct field research on topics such as industrial production, industrial ecology, population ecology, and environmental production or sustainability. | Plan or conduct studies of the ecological implications of historic or projected changes in industrial processes or development. | Prepare plans to manage renewable resources. | Prepare technical and research reports, such as environmental impact reports, and communicate the results to individuals in industry, government, or the general public. | Promote use of environmental management systems (EMS) to reduce waste or to improve environmentally sound use of natural resources. | Provide industrial managers with technical materials on environmental issues, regulatory guidelines, or compliance actions. | Recommend methods to protect the environment or minimize environmental damage from industrial production practices. | Redesign linear, or open-loop, systems into cyclical, or closed-loop, systems so that waste products become inputs for new processes, modeling natural ecosystems. | Research environmental effects of land and water use to determine methods of improving environmental conditions or increasing outputs, such as crop yields. | Research sources of pollution to determine environmental impact or to develop methods of pollution abatement or control. | Review industrial practices, such as the methods and materials used in construction or production, to identify potential liabilities and environmental hazards. | Review research literature to maintain knowledge on topics related to industrial ecology, such as physical science, technology, economy, and public policy. | Translate the theories of industrial ecology into eco-industrial practices.</t>
+          <t>تجزیه و تحلیل تغییرات طراحی‌شده برای بهبود عملکرد محیط‌زیستی سامانه‌های پیچیده و پرهیز از پیامدهای منفی ناخواسته. | به‌کارگیری پژوهش‌های جدید یا موجود درباره بوم‌سازگان‌های طبیعی برای درک سامانه‌های اقتصادی و صنعتی در بستر محیط‌زیست. | ساخت و نگهداری پایگاه‌های داده اطلاعات مربوط به گزینه‌های جایگزین انرژی، آلاینده‌ها، محیط‌های طبیعی، فرایندهای صنعتی و سایر اطلاعات مرتبط با تغییرات بوم‌شناختی. | انجام ارزیابی‌های محیط‌زیستی مطابق با استانداردها، مقررات یا قوانین مربوطه. | انجام تحلیل‌هایی برای تعیین بیشینه کاری که با مقدار معینی انرژی در یک سامانه انجام‌شدنی است، مانند سامانه‌های تولید صنعتی و سامانه‌های تصفیه پسماند. | انجام پژوهش کاربردی درباره آثار فرایندهای صنعتی بر حفاظت، احیا، سیاهه‌برداری، پایش یا بازمعرفی گونه‌ها به محیط طبیعی. | انجام ارزیابی‌های پایداری محیط‌زیستی، با استفاده از فنون تحلیل جریان مواد (MFA) یا تحلیل جریان ماده (SFA). | اجرای پروژه‌های علمی حفاظت، کاهش اثر یا احیا برای پیشگیری از آسیب به منابع، حفظ یکپارچگی زیستگاه‌های حساس و کمینه‌سازی اثر فعالیت‌های انسانی. | ساخت مدل‌های ریاضی پیچیده و پویا از جمعیت، اجتماع زیستی یا سامانه‌های بوم‌شناختی. | تدوین سناریوهای سرمایه‌گذاری در انرژی‌های جایگزین برای مقایسه هزینه‌ها و منافع اقتصادی و محیط‌زیستی. | تدوین یا آزمون پروتکل‌هایی برای پایش اجزای بوم‌سازگان و فرایندهای بوم‌شناختی. | ارزیابی اثربخشی برنامه‌های بوم‌شناسی صنعتی، با استفاده از تحلیل و کاربردهای آماری. | بررسی مصرف و جریان محلی، منطقه‌ای یا جهانی مواد و انرژی در فرایندهای تولید صنعتی. | بررسی مسائل اجتماعی و رابطه آن‌ها با سامانه‌های فنی و محیط‌زیست. | پیش‌بینی وضعیت یا شرایط آینده بوم‌سازگان‌ها، بر پایه تغییر شیوه‌های صنعتی یا شرایط محیط‌زیستی. | شناسایی اثرات محیط‌زیستی ناشی از محصولات، سامانه‌ها یا پروژه‌ها. | شناسایی یا مقایسه اجزای تشکیل‌دهنده یا روابط میان اجزای سامانه‌های صنعتی، اجتماعی و طبیعی. | شناسایی یا تدوین راهبردها یا روش‌هایی برای کمینه‌سازی اثر محیط‌زیستی فرایندهای تولید صنعتی. | شناسایی گزینه‌های پایدار جایگزین برای شیوه‌های صنعتی یا مدیریت پسماند. | بررسی حوادث اثرگذار بر محیط‌زیست برای ارزیابی پیامدهای بوم‌شناختی. | بررسی سازگاری گونه‌های مختلف جانوری و گیاهی با شرایط محیط‌زیستی تغییریافته. | بررسی اثر تغییر مدیریت یا کاربری اراضی بر بوم‌سازگان‌ها. | پایش اثر محیط‌زیستی فعالیت‌های توسعه، آلودگی یا تخریب اراضی. | انجام تحلیل‌هایی برای تعیین اینکه رفتار انسان چگونه بر تغییرات محیط‌زیست اثر می‌گذارد و از آن اثر می‌پذیرد. | انجام تحلیل‌های داده‌ستانده با گسترش محیط‌زیستی (EE I-O). | برنامه‌ریزی یا انجام پژوهش میدانی در موضوعاتی مانند تولید صنعتی، بوم‌شناسی صنعتی، بوم‌شناسی جمعیت و تولید یا پایداری محیط‌زیستی. | برنامه‌ریزی یا انجام مطالعاتی درباره پیامدهای بوم‌شناختی تغییرات تاریخی یا پیش‌بینی‌شده در فرایندهای صنعتی یا توسعه. | تهیه برنامه‌هایی برای مدیریت منابع تجدیدپذیر. | تهیه گزارش‌های فنی و پژوهشی، مانند گزارش‌های ارزیابی اثرات محیط‌زیستی، و انتقال نتایج به افراد فعال در صنعت، دولت یا عموم مردم. | ترویج استفاده از سامانه‌های مدیریت محیط‌زیست (EMS) برای کاهش پسماند یا بهبود استفاده محیط‌زیست‌سازگار از منابع طبیعی. | ارائه مواد فنی درباره مسائل محیط‌زیستی، دستورالعمل‌های نظارتی یا اقدامات انطباق به مدیران صنعتی. | پیشنهاد روش‌هایی برای حفاظت از محیط‌زیست یا کمینه‌سازی آسیب محیط‌زیستی ناشی از شیوه‌های تولید صنعتی. | بازطراحی سامانه‌های خطی یا حلقه‌باز به سامانه‌های چرخه‌ای یا حلقه‌بسته، به‌گونه‌ای که پسماندها به ورودی فرایندهای جدید تبدیل شوند و از بوم‌سازگان‌های طبیعی الگو بگیرند. | پژوهش درباره آثار محیط‌زیستی کاربری زمین و آب برای تعیین روش‌های بهبود شرایط محیط‌زیستی یا افزایش ستانده‌ها، مانند عملکرد محصولات کشاورزی. | پژوهش درباره منابع آلودگی برای تعیین اثر محیط‌زیستی یا تدوین روش‌های کاهش و کنترل آلودگی. | بازبینی شیوه‌های صنعتی، مانند روش‌ها و مواد به‌کاررفته در ساخت یا تولید، برای شناسایی مسئولیت‌های احتمالی و مخاطرات محیط‌زیستی. | بازبینی ادبیات پژوهشی برای به‌روز نگه‌داشتن دانش در موضوعات مرتبط با بوم‌شناسی صنعتی، مانند علوم فیزیکی، فناوری، اقتصاد و سیاست‌گذاری عمومی. | برگردان نظریه‌های بوم‌شناسی صنعتی به شیوه‌های اجرایی بوم‌صنعتی.</t>
         </is>
       </c>
     </row>
@@ -664,42 +664,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geoscientists, Except Hydrologists and Geographers (زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان)</t>
+          <t>زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان (Geoscientists, Except Hydrologists and Geographers)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Engineering Geologist | Environmental Protection Geologist | Exploration Geologist | Geological Specialist | Geologist | Geophysicist | Geoscientist | Mine Geologist | Project Geologist</t>
+          <t>زمین‌شناس مهندسی | زمین‌شناس حفاظت محیط‌زیست | زمین‌شناس اکتشاف | کارشناس زمین‌شناسی | زمین‌شناس | ژئوفیزیک‌دان | دانشمند علوم زمین | زمین‌شناس معدن | زمین‌شناس پروژه</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ACD Systems Canvas | Adobe Acrobat | Adobe Photoshop | Alara CRystalView | نرم‌افزار تست آبخوان | Atoll GeoCAD | Autodesk AutoCAD | BOSS Didger | Bentley Systems gINT | Bilko | ChemStat | Clover Technology GALENA | Compass software | CrystalMaker | نرم‌افزار ثبت داده | نرم‌افزار داده‌کاوی | EPIC GIS | ERDAS ER Mapper | ESRI ArcGIS software | ESRI ArcIMS | ESRI ArcInfo | ESRI ArcView | EarthSoft EQuIS Geology | EarthWorks Downhole Explorer | Earthworks MaxiPit | EasySolve Software SizePerm | نرم‌افزار ایمیل | Enigma software | Evolution Computing EasyCAD | Evolution Computing FastCAD | نرم‌افزار ثبت داده‌های میدانی | Gemcom GEMS | Gemcom Surpac | Geo-Logic Systems LithoTect Interpreter | GeoModel | GeoPLUS Petra | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | سیستم پشتیبانی تحلیل منابع جغرافیایی GRASS | نرم‌افزار GDA تحلیل طراحی ژئومکانیکی | Geosoft DAP server | Geosoft Oasis montaj | Geospatial data abstraction library GDAL | نرم‌افزار GSTAT مدل‌سازی زمین‌آماری | نرم‌افزار زمین‌آماری GS+ | Git | Golden Software Surfer | Gresens 92 | Groundwater Vistas | Groundwater modeling system GMS | HydroSOLVE AQTESOLV | Hydrogeology Basin2 | IHS Energy PowerTools | IRIS Seismic Processing Workshop | Intergraph ImageStation Stereo Softcopy Kit SSK | Interpex IXID | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Landmark Graphics GeoGraphix | Landmark VIP | Leica Geosystems ERDAS IMAGINE | MHC Document Express | MICRODEM | MIT OASES | MJ Systems Logsleuth | MapInfo Professional | نرم‌افزار نقشه‌برداری | Maptek Vulcan | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Midland Valley 3DMove | MineGeo software | MineSight | نرم‌افزار MVSP آمار چندمتغیره | MySQL | National Geophysical Data Center GEODAS | OpenOffice.org | OriginLab Origin | PaleoMag | PaleoTax | Paleontological Statistics PAST | Paradigm SKUA-GOCAD | Parameter Estimation PEST | PolyMap | PowerCAD | Python | RSI ENVI | نرم‌افزار RSI interactive data language IDL | Red Rock DeltaGraph | RockWare ChemFlux | RockWare DepthCon2000 | RockWare Erupt | RockWare FIRSTPIX | RockWare GRADIX | RockWare GeoTrig | RockWare Geochemist's Workbench GWB | RockWare Grav2Dc | RockWare Jlog | RockWare MicroMODEL | RockWare Plan | RockWare Potent | RockWare QuickSyn | RockWare RockPack III | RockWare RockWorks | RockWare Stratbugs | RockWare VEGO | RockWare Visual STUNT | RockWare WinSism | Rockware CrossLog | SACLANTCEN | SAS | Schlumberger Inside Reality | Scientific Software Group FEFLOW | Scientific Software Group Infinite Extent | Scientific Software Group SVHeat | SeeByte SeeTrack | Seismic Micro-Technology KINGDOM | نرم‌افزار تفسیر لرزه‌ای | نرم‌افزار تجسم لرزه‌ای | Shape software | Socorro Scientific Software Refract2K | Solvcalv | Starpint Software Super Slug | StrainSim | Systat Software SigmaStat | TECHBASE | نرم‌افزار نقشه‌برداری سطح زمین | The MathWorks MATLAB | Trimble Terramodel | Triton Elics International SeaClass | Upperspace DesignCAD | Upperspace ModelCAD | Waterloo Hydrogeologic AquaChem | Waterloo Hydrogeologic FlowPath II | نرم‌افزار لاگ‌گیری چاه</t>
+          <t>ACD Systems Canvas | Adobe Acrobat | Adobe Photoshop | Alara CRystalView | نرم‌افزار تست آبخوان | Atoll GeoCAD | Autodesk AutoCAD | BOSS Didger | Bentley Systems gINT | Bilko | ChemStat | Clover Technology GALENA | Compass software | CrystalMaker | نرم‌افزار ثبت داده | نرم‌افزار داده‌کاوی | EPIC GIS | ERDAS ER Mapper | نرم‌افزار ESRI ArcGIS | ESRI ArcIMS | ESRI ArcInfo | ESRI ArcView | EarthSoft EQuIS Geology | EarthWorks Downhole Explorer | Earthworks MaxiPit | EasySolve Software SizePerm | نرم‌افزار ایمیل | Enigma software | Evolution Computing EasyCAD | Evolution Computing FastCAD | نرم‌افزار ثبت داده‌های میدانی | Gemcom GEMS | Gemcom Surpac | Geo-Logic Systems LithoTect Interpreter | GeoModel | GeoPLUS Petra | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | سیستم پشتیبانی تحلیل منابع جغرافیایی GRASS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | Geosoft DAP server | Geosoft Oasis montaj | Geospatial data abstraction library GDAL | نرم‌افزار GSTAT مدل‌سازی زمین‌آماری | نرم‌افزار زمین‌آماری GS+ | Git | Golden Software Surfer | Gresens 92 | Groundwater Vistas | Groundwater modeling system GMS | HydroSOLVE AQTESOLV | Hydrogeology Basin2 | IHS Energy PowerTools | IRIS Seismic Processing Workshop | Intergraph ImageStation Stereo Softcopy Kit SSK | Interpex IXID | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Landmark Graphics GeoGraphix | Landmark VIP | Leica Geosystems ERDAS IMAGINE | MHC Document Express | MICRODEM | MIT OASES | MJ Systems Logsleuth | MapInfo Professional | نرم‌افزار نقشه‌برداری | Maptek Vulcan | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Word | Midland Valley 3DMove | MineGeo software | MineSight | نرم‌افزار برنامه آماری چندمتغیره MVSP | MySQL | National Geophysical Data Center GEODAS | OpenOffice.org | OriginLab Origin | PaleoMag | PaleoTax | Paleontological Statistics PAST | Paradigm SKUA-GOCAD | Parameter Estimation PEST | PolyMap | PowerCAD | Python | RSI ENVI | RSI interactive data language IDL software | Red Rock DeltaGraph | RockWare ChemFlux | RockWare DepthCon2000 | RockWare Erupt | RockWare FIRSTPIX | RockWare GRADIX | RockWare GeoTrig | RockWare Geochemist's Workbench GWB | RockWare Grav2Dc | RockWare Jlog | RockWare MicroMODEL | RockWare Plan | RockWare Potent | RockWare QuickSyn | RockWare RockPack III | RockWare RockWorks | RockWare Stratbugs | RockWare VEGO | RockWare Visual STUNT | RockWare WinSism | Rockware CrossLog | SACLANTCEN | SAS | Schlumberger Inside Reality | Scientific Software Group FEFLOW | Scientific Software Group Infinite Extent | Scientific Software Group SVHeat | SeeByte SeeTrack | Seismic Micro-Technology KINGDOM | نرم‌افزار تفسیر لرزه‌ای | نرم‌افزار تجسم لرزه‌ای | Shape software | Socorro Scientific Software Refract2K | Solvcalv | Starpint Software Super Slug | StrainSim | Systat Software SigmaStat | TECHBASE | نرم‌افزار نقشه‌برداری سطح زمین | The MathWorks MATLAB | Trimble Terramodel | Triton Elics International SeaClass | Upperspace DesignCAD | Upperspace ModelCAD | Waterloo Hydrogeologic AquaChem | Waterloo Hydrogeologic FlowPath II | نرم‌افزار لاگ‌گیری چاه</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Critical Thinking | Science | Speaking | Active Listening | Writing | Mathematics | Active Learning | Learning Strategies | Monitoring</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Geography | Mathematics | English Language | Chemistry | Physics | Computers and Electronics | Education and Training | Engineering and Technology</t>
+          <t>جغرافیا | ریاضیات | زبان انگلیسی | شیمی | فیزیک | رایانه و الکترونیک | آموزش و پرورش | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Written Comprehension | Inductive Reasoning | Oral Comprehension | Oral Expression | Written Expression | Problem Sensitivity | Deductive Reasoning | Category Flexibility | Information Ordering | Mathematical Reasoning | Speech Clarity | Near Vision | Speech Recognition | Fluency of Ideas | Number Facility | Flexibility of Closure | Far Vision | Originality | Selective Attention | Visualization | Perceptual Speed</t>
+          <t>درک کتبی | استدلال استقرایی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال ریاضی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری بستار | بینایی دور | اصالت | توجه انتخابی | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Telephone Conversations | Determine Tasks, Priorities and Goals | Work With or Contribute to a Work Group or Team | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Contact With Others | Spend Time Sitting</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Astronomers | Atmospheric and Space Scientists | Biologists | Conservation Scientists | Data Scientists | Environmental Restoration Planners | Environmental Science and Protection Technicians, Including Health | Environmental Scientists and Specialists, Including Health | Geodetic Surveyors | Geographers | Geological Technicians, Except Hydrologic Technicians | Hydrologic Technicians | Hydrologists | Industrial Ecologists | Mining and Geological Engineers, Including Mining Safety Engineers | Petroleum Engineers | Soil and Plant Scientists | Surveying and Mapping Technicians | Surveyors | Water Resource Specialists</t>
+          <t>اخترشناسان | دانشمندان علوم جوی و فضایی | زیست‌شناسان | دانشمندان حفاظت | دانشمندان داده | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | نقشه‌برداران ژئودتیک | جغرافیدانان | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | آب‌شناسان | بوم‌شناسان صنعتی | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | مهندسان نفت | دانشمندان خاک و گیاه | تکنسین‌های نقشه‌برداری و نقشه‌کشی | نقشه‌برداران | متخصصان منابع آب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Advise construction firms or government agencies on dam or road construction, foundation design, land use, or resource management. | Analyze and interpret geological data, using computer software. | Analyze and interpret geological, geochemical, or geophysical information from sources, such as survey data, well logs, bore holes, or aerial photos. | Assess ground or surface water movement to provide advice on issues, such as waste management, route and site selection, or the restoration of contaminated sites. | Collaborate with medical or health researchers to address health problems related to geological materials or processes. | Communicate geological findings by writing research papers, participating in conferences, or teaching geological science at universities. | Conduct geological or geophysical studies to provide information for use in regional development, site selection, or development of public works projects. | Design geological mine maps, monitor mine structural integrity, or advise and monitor mining crews. | Determine methods to incorporate geomethane or methane hydrates into global energy production or evaluate the potential environmental impacts of such incorporation. | Determine ways to mitigate the negative consequences of mineral dust dispersion. | Develop applied software for the analysis and interpretation of geological data. | Develop strategies for more environmentally friendly resource extraction and reclamation. | Develop ways to capture or use gases burned off as waste during oil production processes. | Identify deposits of construction materials suitable for use as concrete aggregates, road fill, or other applications. | Identify new sources of platinum group elements for industrial applications, such as automotive fuel cells or pollution abatement systems. | Identify possible sites for carbon sequestration projects. | Identify risks for natural disasters, such as mudslides, earthquakes, or volcanic eruptions. | Inspect construction projects to analyze engineering problems, using test equipment or drilling machinery. | Investigate the composition, structure, or history of the Earth's crust through the collection, examination, measurement, or classification of soils, minerals, rocks, or fossil remains. | Locate and estimate probable natural gas, oil, or mineral ore deposits or underground water resources, using aerial photographs, charts, or research or survey results. | Locate and review research articles or environmental, historical, or technical reports. | Locate potential sources of geothermal energy. | Measure characteristics of the Earth, such as gravity or magnetic fields, using equipment such as seismographs, gravimeters, torsion balances, or magnetometers. | Plan or conduct geological, geochemical, or geophysical field studies or surveys, sample collection, or drilling and testing programs used to collect data for research or application. | Prepare geological maps, cross-sectional diagrams, charts, or reports concerning mineral extraction, land use, or resource management, using results of fieldwork or laboratory research. | Provide advice on the safe siting of new nuclear reactor projects or methods of nuclear waste management. | Research geomechanical or geochemical processes to be used in carbon sequestration projects. | Research ways to reduce the ecological footprint of increasingly prevalent megacities. | Review environmental, historical, or technical reports and publications for accuracy. | Review work plans to determine the effectiveness of activities for mitigating soil or groundwater contamination. | Study historical climate change indicators found in locations, such as ice sheets or rock formations to develop climate change models. | Test industrial diamonds or abrasives, soil, or rocks to determine their geological characteristics, using optical, x-ray, heat, acid, or precision instruments.</t>
+          <t>ارائه مشاوره به شرکت‌های ساختمانی یا نهادهای دولتی درباره ساخت سد یا جاده، طراحی پی، کاربری زمین یا مدیریت منابع. | تجزیه و تحلیل و تفسیر داده‌های زمین‌شناسی، با استفاده از نرم‌افزارهای رایانه‌ای. | تجزیه و تحلیل و تفسیر اطلاعات زمین‌شناسی، ژئوشیمیایی یا ژئوفیزیکی از منابعی مانند داده‌های نقشه‌برداری، نگارهای چاه، گمانه‌ها یا عکس‌های هوایی. | ارزیابی حرکت آب‌های زیرزمینی یا سطحی برای ارائه مشاوره در موضوعاتی مانند مدیریت پسماند، انتخاب مسیر و محل، یا احیای محل‌های آلوده. | همکاری با پژوهشگران پزشکی یا سلامت برای رسیدگی به مشکلات سلامت مرتبط با مواد یا فرایندهای زمین‌شناختی. | انتقال یافته‌های زمین‌شناختی از راه نگارش مقالات پژوهشی، شرکت در همایش‌ها یا تدریس علوم زمین در دانشگاه‌ها. | انجام مطالعات زمین‌شناسی یا ژئوفیزیکی برای فراهم کردن اطلاعات مورد استفاده در توسعه منطقه‌ای، انتخاب محل یا اجرای پروژه‌های عمرانی. | طراحی نقشه‌های زمین‌شناسی معدن، پایش یکپارچگی سازه‌ای معدن، یا مشاوره و نظارت بر گروه‌های معدن‌کاری. | تعیین روش‌های وارد کردن ژئومتان یا هیدرات‌های متان به تولید جهانی انرژی یا ارزیابی پیامدهای محیط‌زیستی احتمالی این کار. | تعیین راه‌های کاهش پیامدهای منفی پراکنش گردوغبار معدنی. | توسعه نرم‌افزارهای کاربردی برای تجزیه و تحلیل و تفسیر داده‌های زمین‌شناسی. | تدوین راهبردهایی برای استخراج و احیای منابع با سازگاری بیشتر با محیط‌زیست. | تدوین روش‌هایی برای مهار یا استفاده از گازهایی که در فرایند تولید نفت به‌صورت پسماند سوزانده می‌شوند. | شناسایی ذخایر مصالح ساختمانی مناسب برای استفاده به‌عنوان سنگدانه بتن، خاکریز جاده یا سایر کاربردها. | شناسایی منابع جدید عناصر گروه پلاتین برای کاربردهای صنعتی، مانند پیل‌های سوختی خودرو یا سامانه‌های کاهش آلودگی. | شناسایی محل‌های ممکن برای پروژه‌های ترسیب کربن. | شناسایی مخاطرات بلایای طبیعی، مانند رانش زمین، زمین‌لرزه یا فوران آتشفشان. | بازرسی پروژه‌های ساختمانی برای تحلیل مسائل مهندسی، با استفاده از تجهیزات آزمون یا ماشین‌آلات حفاری. | بررسی ترکیب، ساختار یا تاریخچه پوسته زمین از راه گردآوری، بررسی، اندازه‌گیری یا طبقه‌بندی خاک‌ها، کانی‌ها، سنگ‌ها یا بقایای فسیلی. | مکان‌یابی و برآورد ذخایر احتمالی گاز طبیعی، نفت یا کانه‌های معدنی یا منابع آب زیرزمینی، با استفاده از عکس‌های هوایی، نمودارها یا نتایج پژوهش و نقشه‌برداری. | یافتن و بازبینی مقالات پژوهشی یا گزارش‌های محیط‌زیستی، تاریخی یا فنی. | مکان‌یابی منابع بالقوه انرژی زمین‌گرمایی. | اندازه‌گیری ویژگی‌های زمین، مانند گرانش یا میدان‌های مغناطیسی، با استفاده از تجهیزاتی مانند لرزه‌نگار، گرانی‌سنج، ترازوی پیچشی یا مغناطیس‌سنج. | برنامه‌ریزی یا انجام مطالعات و نقشه‌برداری‌های میدانی زمین‌شناسی، ژئوشیمیایی یا ژئوفیزیکی، نمونه‌برداری، یا برنامه‌های حفاری و آزمون که برای گردآوری داده‌های پژوهشی یا کاربردی به کار می‌روند. | تهیه نقشه‌های زمین‌شناسی، نمودارهای مقطعی، چارت‌ها یا گزارش‌های مربوط به استخراج مواد معدنی، کاربری زمین یا مدیریت منابع، با استفاده از نتایج کار میدانی یا پژوهش آزمایشگاهی. | ارائه مشاوره درباره مکان‌یابی ایمن پروژه‌های راکتور هسته‌ای جدید یا روش‌های مدیریت پسماند هسته‌ای. | پژوهش درباره فرایندهای ژئومکانیکی یا ژئوشیمیایی برای استفاده در پروژه‌های ترسیب کربن. | پژوهش درباره راه‌های کاهش ردپای بوم‌شناختی کلان‌شهرهایی که روزبه‌روز فراگیرتر می‌شوند. | بازبینی گزارش‌ها و انتشارات محیط‌زیستی، تاریخی یا فنی از نظر صحت. | بازبینی برنامه‌های کاری برای تعیین اثربخشی فعالیت‌های کاهش آلودگی خاک یا آب زیرزمینی. | مطالعه شاخص‌های تاریخی تغییر اقلیم موجود در مکان‌هایی مانند پوشش‌های یخی یا سازندهای سنگی برای تدوین مدل‌های تغییر اقلیم. | آزمون الماس‌ها یا ساینده‌های صنعتی، خاک یا سنگ برای تعیین ویژگی‌های زمین‌شناختی آن‌ها، با استفاده از ابزارهای نوری، پرتو ایکس، حرارتی، اسیدی یا دقیق.</t>
         </is>
       </c>
     </row>
@@ -721,42 +721,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hydrologists (آب‌شناسان)</t>
+          <t>آب‌شناسان (Hydrologists)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Groundwater Consultant | Hydrogeologist | Hydrologist | Physical Scientist | Research Hydrologist | Scientist | Source Water Protection Specialist</t>
+          <t>مشاور آب زیرزمینی | هیدروژئولوژیست | آب‌شناس | دانشمند علوم فیزیکی | آب‌شناس پژوهشی | دانشمند | کارشناس حفاظت از منابع آب</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Advanced Logic Technology WellCAD | Amtec Engineering Tecplot | Argus ONE Open Numerical Environments | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk AutoCAD Map 3D | Autodesk Land Desktop | BOSS International Visual Groundwater | Bentley MicroStation | Bentley Systems gINT | نرم‌افزار مدل‌سازی جریان و انتقال زیست‌تخریب‌پذیری | C++ | Carlson SurvCADD | ChemStat | Clover Technology GALENA | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | ESRI ArcGIS software | ESRI ArcView | EarthSoft EQuIS Geology | EarthVision | Electric Rain Swift 3D | نرم‌افزار ایمیل | EnviroData Solutions | EnviroInsite | Environmental Software and Services SUTRA | Fitts Geosolutions TWODAN | Formlink HydroGEN | Formula translation/translator FORTRAN | GAEA Technologies Packet ESA | GAEA Technologies WinLog | GAEA Technologies WinSieve | GIS/Solutions GIS/Key | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار GDA تحلیل طراحی ژئومکانیکی | Golden Software Strater | Golden Software Surfer | نرم‌افزار گرافیکی | Groundwater Software QuickCross/Fence | Groundwater Software QuickLog | Groundwater Software Visual Site Manager | Groundwater Vistas | Groundwater modeling system GMS | HEC-1 | HEC-2 | HEC-HMS | HEC-RAS | HydroSOLVE AQTESOLV | نرم‌افزار شبیه‌سازی هیدرولوژیکی HSPF | Integrated Environmental Services 3D Master | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Logger data manager LDM | Logplot software | MLPU | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Windows Vista Business | Microsoft Word | نرم‌افزار انطباق NPDES | PRINCE | Parameter Estimation PEST | Python | R | RIVERMorph | نرم‌افزار معادله جهانی اصلاح‌شده فرسایش خاک RUSLE | River Lake Altimetry Product | RockWare ChemFlux | RockWare Geochemist's Workbench GWB | RockWare MODFLOW | RockWare RockWorks | RockWare SieveGraph | SEDCAD | نرم‌افزار پایگاه داده ماهواره‌ای | Scientific Software Group 3DFATMIC | Scientific Software Group 3DFEMFAT | Scientific Software Group AQUA3D | Scientific Software Group AQUASEA | Scientific Software Group AQUIPACK | Scientific Software Group AT123D | Scientific Software Group AquaDyn | Scientific Software Group Aquifer win32 | Scientific Software Group BIO1D | Scientific Software Group BIOF&amp;T | Scientific Software Group BIOSLURP | Scientific Software Group BioTrends | Scientific Software Group CHASM | Scientific Software Group ChemGraph | Scientific Software Group DTM | Scientific Software Group EVS | Scientific Software Group Enviro-Base Pro | Scientific Software Group EnviroScape | Scientific Software Group FEFLOW | Scientific Software Group Filter Drain FD | Scientific Software Group GFLOW | Scientific Software Group HYDROGEOCHEM | Scientific Software Group HydroGeo Analyst | Scientific Software Group Infinite Extent | Scientific Software Group MARS 2-D/3-D | Scientific Software Group MIDUSS | Scientific Software Group MIGRATE | Scientific Software Group MINTEQA2 | Scientific Software Group MOCDENSE | Scientific Software Group MODFLOWT | Scientific Software Group MODPUMP | Scientific Software Group MODRET | Scientific Software Group MOFAT | Scientific Software Group MOVER | Scientific Software Group MS-VMS | Scientific Software Group MT3D99 | Scientific Software Group MohrView | Scientific Software Group OILVOL | Scientific Software Group POLLUTE | Scientific Software Group QHM | Scientific Software Group QuickSoil | Scientific Software Group RISC WorkBench | Scientific Software Group RMT | Scientific Software Group SEQUENCE | Scientific Software Group SESOIL | Scientific Software Group SLAEM/MLAEM | Scientific Software Group SOILPARA | Scientific Software Group SOLUTRANS | Scientific Software Group SURF | Scientific Software Group SVFlux | Scientific Software Group SVHeat | Scientific Software Group Soil Vapor Extraction BioSVE | Scientific Software Group StepMaster | Scientific Software Group TUFLOW | Scientific Software Group VAM2D | Scientific Software Group WinFlow | Scientific Software Group WinTran | Scientific Software GroupWHI UnSAT Suite | Scientific Software GroupWinFence | Softree Technical Systems Terrain Tools | SoilVision Systems SVGrainsize | SoilVision Systems SVOFFICE | Starpint Software Super Slug | StatPoint StatGraphics Plus | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مدل‌سازی آب‌های سطحی SMS | The MathWorks MATLAB | Trimble Pathfinder Office | Trimble TerraSync | Vieux &amp; Associates Vflow | Visual MODFLOW Pro | Waterloo Hydrogeologic AquaChem | Waterloo Hydrogeologic AquiferTest Pro | Waterloo Hydrogeologic RBC Tier 2 Analyzer | نرم‌افزار مدل‌سازی حوضه آبریز WMS | نرم‌افزار مرورگر وب</t>
+          <t>Advanced Logic Technology WellCAD | Amtec Engineering Tecplot | Argus ONE Open Numerical Environments | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk AutoCAD Map 3D | Autodesk Land Desktop | BOSS International Visual Groundwater | Bentley MicroStation | Bentley Systems gINT | نرم‌افزار مدل‌سازی جریان و انتقال زیست‌تخریب‌پذیری | C++ | Carlson SurvCADD | ChemStat | Clover Technology GALENA | نرم‌افزار تجسم داده | نرم‌افزار پایگاه داده | نرم‌افزار ESRI ArcGIS | ESRI ArcView | EarthSoft EQuIS Geology | EarthVision | Electric Rain Swift 3D | نرم‌افزار ایمیل | EnviroData Solutions | EnviroInsite | Environmental Software and Services SUTRA | Fitts Geosolutions TWODAN | Formlink HydroGEN | Formula translation/translator FORTRAN | GAEA Technologies Packet ESA | GAEA Technologies WinLog | GAEA Technologies WinSieve | GIS/Solutions GIS/Key | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تحلیل طراحی ژئومکانیکی GDA | Golden Software Strater | Golden Software Surfer | نرم‌افزار گرافیکی | Groundwater Software QuickCross/Fence | Groundwater Software QuickLog | Groundwater Software Visual Site Manager | Groundwater Vistas | Groundwater modeling system GMS | HEC-1 | HEC-2 | HEC-HMS | HEC-RAS | HydroSOLVE AQTESOLV | نرم‌افزار برنامه شبیه‌سازی هیدرولوژیکی فرترن HSPF | Integrated Environmental Services 3D Master | سیستم مدیریت اطلاعات آزمایشگاهی LIMS | Logger data manager LDM | Logplot software | MLPU | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visual Basic | Microsoft Windows Vista Business | Microsoft Word | نرم‌افزار انطباق NPDES | PRINCE | Parameter Estimation PEST | Python | R | RIVERMorph | نرم‌افزار معادله جهانی اصلاح‌شده فرسایش خاک RUSLE | River Lake Altimetry Product | RockWare ChemFlux | RockWare Geochemist's Workbench GWB | RockWare MODFLOW | RockWare RockWorks | RockWare SieveGraph | SEDCAD | نرم‌افزار پایگاه داده ماهواره‌ای | Scientific Software Group 3DFATMIC | Scientific Software Group 3DFEMFAT | Scientific Software Group AQUA3D | Scientific Software Group AQUASEA | Scientific Software Group AQUIPACK | Scientific Software Group AT123D | Scientific Software Group AquaDyn | Scientific Software Group Aquifer win32 | Scientific Software Group BIO1D | Scientific Software Group BIOF&amp;T | Scientific Software Group BIOSLURP | Scientific Software Group BioTrends | Scientific Software Group CHASM | Scientific Software Group ChemGraph | Scientific Software Group DTM | Scientific Software Group EVS | Scientific Software Group Enviro-Base Pro | Scientific Software Group EnviroScape | Scientific Software Group FEFLOW | Scientific Software Group Filter Drain FD | Scientific Software Group GFLOW | Scientific Software Group HYDROGEOCHEM | Scientific Software Group HydroGeo Analyst | Scientific Software Group Infinite Extent | Scientific Software Group MARS 2-D/3-D | Scientific Software Group MIDUSS | Scientific Software Group MIGRATE | Scientific Software Group MINTEQA2 | Scientific Software Group MOCDENSE | Scientific Software Group MODFLOWT | Scientific Software Group MODPUMP | Scientific Software Group MODRET | Scientific Software Group MOFAT | Scientific Software Group MOVER | Scientific Software Group MS-VMS | Scientific Software Group MT3D99 | Scientific Software Group MohrView | Scientific Software Group OILVOL | Scientific Software Group POLLUTE | Scientific Software Group QHM | Scientific Software Group QuickSoil | Scientific Software Group RISC WorkBench | Scientific Software Group RMT | Scientific Software Group SEQUENCE | Scientific Software Group SESOIL | Scientific Software Group SLAEM/MLAEM | Scientific Software Group SOILPARA | Scientific Software Group SOLUTRANS | Scientific Software Group SURF | Scientific Software Group SVFlux | Scientific Software Group SVHeat | Scientific Software Group Soil Vapor Extraction BioSVE | Scientific Software Group StepMaster | Scientific Software Group TUFLOW | Scientific Software Group VAM2D | Scientific Software Group WinFlow | Scientific Software Group WinTran | Scientific Software GroupWHI UnSAT Suite | Scientific Software GroupWinFence | Softree Technical Systems Terrain Tools | SoilVision Systems SVGrainsize | SoilVision Systems SVOFFICE | Starpint Software Super Slug | StatPoint StatGraphics Plus | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار مدل‌سازی آب‌های سطحی SMS | The MathWorks MATLAB | Trimble Pathfinder Office | Trimble TerraSync | Vieux &amp; Associates Vflow | Visual MODFLOW Pro | Waterloo Hydrogeologic AquaChem | Waterloo Hydrogeologic AquiferTest Pro | Waterloo Hydrogeologic RBC Tier 2 Analyzer | نرم‌افزار مدل‌سازی حوضه آبریز WMS | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Critical Thinking | Science | Reading Comprehension | Active Listening | Speaking | Mathematics | Writing | Active Learning | Monitoring | Learning Strategies</t>
+          <t>تفکر انتقادی | علوم | درک مطلب | گوش دادن فعال | سخن گفتن | ریاضیات | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mathematics | Physics | Engineering and Technology | English Language | Geography | Computers and Electronics | Chemistry | Biology</t>
+          <t>ریاضیات | فیزیک | مهندسی و فناوری | زبان انگلیسی | جغرافیا | رایانه و الکترونیک | شیمی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Mathematical Reasoning | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Category Flexibility | Near Vision | Flexibility of Closure | Information Ordering | Speech Recognition | Speech Clarity | Fluency of Ideas | Originality | Number Facility | Perceptual Speed | Far Vision | Visualization</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال ریاضی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | توانایی عددی | سرعت ادراکی | بینایی دور | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>E-Mail | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Work With or Contribute to a Work Group or Team | Importance of Being Exact or Accurate | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Indoors, Environmentally Controlled | Contact With Others | Spend Time Sitting | Level of Competition</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | ارتباط با دیگران | صرف زمان برای نشستن | سطح رقابت</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Atmospheric and Space Scientists | Biologists | Brownfield Redevelopment Specialists and Site Managers | Climate Change Policy Analysts | Conservation Scientists | Environmental Engineering Technologists and Technicians | Environmental Engineers | Environmental Restoration Planners | Environmental Science and Protection Technicians, Including Health | Environmental Scientists and Specialists, Including Health | Geodetic Surveyors | Geological Technicians, Except Hydrologic Technicians | Geoscientists, Except Hydrologists and Geographers | Hydrologic Technicians | Industrial Ecologists | Mining and Geological Engineers, Including Mining Safety Engineers | Petroleum Engineers | Soil and Plant Scientists | Water Resource Specialists | Water/Wastewater Engineers</t>
+          <t>دانشمندان علوم جوی و فضایی | زیست‌شناسان | متخصصان بازآفرینی زمین‌های قهوه‌ای و مدیران سایت | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان حفاظت | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط‌زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | نقشه‌برداران ژئودتیک | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | تکنسین‌های هیدرولوژی | بوم‌شناسان صنعتی | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | مهندسان نفت | دانشمندان خاک و گیاه | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Administer programs designed to ensure the proper sealing of abandoned wells. | Answer questions and provide technical assistance and information to contractors or the public regarding issues such as well drilling, code requirements, hydrology, and geology. | Apply research findings to help minimize the environmental impacts of pollution, waterborne diseases, erosion, and sedimentation. | Collect and analyze water samples as part of field investigations or to validate data from automatic monitors. | Compile and evaluate hydrologic information to prepare navigational charts and maps and to predict atmospheric conditions. | Conduct research and communicate information to promote the conservation and preservation of water resources. | Conduct short- and long-term climate assessments and study storm occurrences. | Coordinate and supervise the work of professional and technical staff, including research assistants, technologists, and technicians. | Design and conduct scientific hydrogeological investigations to ensure that accurate and appropriate information is available for use in water resource management decisions. | Design civil works associated with hydrographic activities and supervise their construction, installation, and maintenance. | Develop computer models for hydrologic predictions. | Develop or modify methods for conducting hydrologic studies. | Evaluate data and provide recommendations regarding the feasibility of municipal projects, such as hydroelectric power plants, irrigation systems, flood warning systems, and waste treatment facilities. | Evaluate research data in terms of its impact on issues such as soil and water conservation, flood control planning, and water supply forecasting. | Install, maintain, and calibrate instruments such as those that monitor water levels, rainfall, and sediments. | Investigate complaints or conflicts related to the alteration of public waters, gathering information, recommending alternatives, informing participants of progress, and preparing draft orders. | Investigate properties, origins, and activities of glaciers, ice, snow, and permafrost. | Measure and graph phenomena such as lake levels, stream flows, and changes in water volumes. | Monitor the work of well contractors, exploratory borers, and engineers and enforce rules regarding their activities. | Prepare hydrogeologic evaluations of known or suspected hazardous waste sites and land treatment and feedlot facilities. | Prepare written and oral reports describing research results, using illustrations, maps, appendices, and other information. | Review applications for site plans and permits and recommend approval, denial, modification, or further investigative action. | Study and analyze the physical aspects of the earth in terms of hydrological components, including atmosphere, hydrosphere, and interior structure. | Study and document quantities, distribution, disposition, and development of underground and surface waters. | Study public water supply issues, including flood and drought risks, water quality, wastewater, and impacts on wetland habitats.</t>
+          <t>اداره برنامه‌هایی که برای اطمینان از مسدودسازی صحیح چاه‌های متروکه طراحی شده‌اند. | پاسخ‌گویی به پرسش‌ها و ارائه کمک و اطلاعات فنی به پیمانکاران یا عموم مردم درباره موضوعاتی مانند حفر چاه، الزامات آیین‌نامه‌ای، آب‌شناسی و زمین‌شناسی. | به‌کارگیری یافته‌های پژوهشی برای کمک به کمینه‌سازی اثرات محیط‌زیستی آلودگی، بیماری‌های منتقله از آب، فرسایش و رسوب‌گذاری. | گردآوری و تجزیه و تحلیل نمونه‌های آب در چارچوب بررسی‌های میدانی یا برای اعتبارسنجی داده‌های پایشگرهای خودکار. | گردآوری و ارزیابی اطلاعات آب‌شناختی برای تهیه نقشه‌ها و چارت‌های ناوبری و پیش‌بینی شرایط جوی. | انجام پژوهش و انتقال اطلاعات برای ترویج حفاظت و صیانت از منابع آب. | انجام ارزیابی‌های اقلیمی کوتاه‌مدت و بلندمدت و مطالعه رخداد توفان‌ها. | هماهنگی و سرپرستی کار کارکنان متخصص و فنی، از جمله دستیاران پژوهشی، تکنولوژیست‌ها و تکنسین‌ها. | طراحی و انجام بررسی‌های علمی هیدروژئولوژیکی برای اطمینان از در دسترس بودن اطلاعات دقیق و مناسب جهت استفاده در تصمیم‌های مدیریت منابع آب. | طراحی سازه‌های عمرانی مرتبط با فعالیت‌های آب‌نگاری و سرپرستی ساخت، نصب و نگهداری آن‌ها. | تدوین مدل‌های رایانه‌ای برای پیش‌بینی‌های آب‌شناختی. | تدوین یا اصلاح روش‌های انجام مطالعات آب‌شناختی. | ارزیابی داده‌ها و ارائه توصیه درباره امکان‌پذیری پروژه‌های شهری، مانند نیروگاه‌های برق‌آبی، سامانه‌های آبیاری، سامانه‌های هشدار سیل و تأسیسات تصفیه پسماند. | ارزیابی داده‌های پژوهشی از نظر اثر آن‌ها بر موضوعاتی مانند حفاظت خاک و آب، برنامه‌ریزی مهار سیل و پیش‌بینی تأمین آب. | نصب، نگهداری و کالیبراسیون ابزارهایی مانند دستگاه‌های پایش تراز آب، بارش و رسوب. | بررسی شکایت‌ها یا اختلافات مرتبط با تغییر در آب‌های عمومی، شامل گردآوری اطلاعات، پیشنهاد گزینه‌های جایگزین، آگاه‌سازی طرف‌ها از پیشرفت کار و تهیه پیش‌نویس دستورها. | بررسی ویژگی‌ها، خاستگاه و رفتار یخچال‌های طبیعی، یخ، برف و خاک‌های همیشه‌یخ. | اندازه‌گیری و ترسیم نمودار پدیده‌هایی مانند تراز دریاچه‌ها، دبی رودخانه‌ها و تغییرات حجم آب. | پایش کار پیمانکاران حفر چاه، حفاران اکتشافی و مهندسان و اعمال مقررات مربوط به فعالیت آنان. | تهیه ارزیابی‌های هیدروژئولوژیکی محل‌های شناخته‌شده یا مظنون به پسماند خطرناک و تأسیسات تصفیه زمینی و دامداری‌های متمرکز. | تهیه گزارش‌های کتبی و شفاهی برای تشریح نتایج پژوهش، با استفاده از تصاویر، نقشه‌ها، پیوست‌ها و سایر اطلاعات. | بازبینی درخواست‌های طرح‌های مکانی و مجوزها و ارائه توصیه درباره تأیید، رد، اصلاح یا انجام بررسی بیشتر. | مطالعه و تجزیه و تحلیل جنبه‌های فیزیکی زمین از نظر مؤلفه‌های آب‌شناختی، شامل جو، آب‌کره و ساختار درونی. | مطالعه و مستندسازی مقدار، توزیع، وضعیت و توسعه آب‌های زیرزمینی و سطحی. | مطالعه مسائل تأمین آب عمومی، از جمله خطر سیل و خشک‌سالی، کیفیت آب، فاضلاب و اثرات آن بر زیستگاه‌های تالابی.</t>
         </is>
       </c>
     </row>
@@ -778,12 +778,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Physical Scientists, All Other (دانشمندان علوم فیزیکی، سایر)</t>
+          <t>دانشمندان علوم فیزیکی، سایر (Physical Scientists, All Other)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Environmental Chemist | Geophysicist | Metallurgist | Nuclear Scientist | Oceanographer | Optical Scientist | Physical Scientist | Planetary Scientist | Research Physicist | Spectroscopist</t>
+          <t>شیمی‌دان محیط‌زیست | ژئوفیزیک‌دان | متالورژیست | دانشمند هسته‌ای | اقیانوس‌شناس | دانشمند اپتیک | دانشمند علوم فیزیکی | دانشمند علوم سیاره‌ای | فیزیکدان پژوهشی | متخصص طیف‌سنجی</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -793,27 +793,27 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Critical Thinking | Mathematics | Active Learning | Writing | Speaking | Active Listening | Science | Monitoring</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Physics | Chemistry | Mathematics | English Language | Computers and Electronics | Engineering and Technology | Education and Training | Geography | Administration and Management</t>
+          <t>فیزیک | شیمی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مهندسی و فناوری | آموزش و پرورش | جغرافیا | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Deductive Reasoning | Inductive Reasoning | Information Ordering | Problem Sensitivity | Near Vision | Speech Clarity | Speech Recognition | Category Flexibility | Fluency of Ideas | Originality | Selective Attention | Time Sharing | Visualization | Memorization | Mathematical Reasoning | Number Facility | Perceptual Speed | Flexibility of Closure</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>E-Mail | Telephone Conversations | Face-to-Face Discussions with Individuals and Within Teams | Indoors, Environmentally Controlled | Spend Time Sitting | Contact With Others | Work With or Contribute to a Work Group or Team | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Time Pressure | Wear Common Protective or Safety Equipment such as Safety Shoes, Glasses, Gloves, Hearing Protection, Hard Hats, or Life Jackets | Exposed to Hazardous Conditions | Spend Time Standing | Spend Time Using Your Hands to Handle, Control, or Feel Objects, Tools, or Controls | Consequence of Error | Importance of Repeating Same Tasks</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | قرار گرفتن در معرض شرایط خطرناک | صرف زمان برای ایستادن | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | پیامد خطا | اهمیت تکرار وظایف یکسان</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chemists | Materials Scientists | Physicists | Astronomers | Atmospheric and Space Scientists | Geoscientists, Except Hydrologists and Geographers | Hydrologists | Environmental Scientists and Specialists, Including Health | Remote Sensing Scientists and Technologists | Industrial Ecologists | Environmental Restoration Planners | Climate Change Policy Analysts | Chemical Technicians | Nuclear Technicians | Geological Technicians, Except Hydrologic Technicians | Chemistry Teachers, Postsecondary | Physics Teachers, Postsecondary | Natural Sciences Managers | Materials Engineers | Nuclear Engineers</t>
+          <t>شیمی‌دانان | دانشمندان مواد | فیزیکدانان | اخترشناسان | دانشمندان علوم جوی و فضایی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | آب‌شناسان | دانشمندان و متخصصان محیط زیست، شامل بهداشت | دانشمندان و فناوران سنجش از دور | بوم‌شناسان صنعتی | برنامه‌ریزان احیای محیط‌زیست | تحلیل‌گران سیاست تغییرات اقلیمی | تکنسین‌های شیمی | تکنسین‌های هسته‌ای | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | مدرسان شیمی، پس از متوسطه | مدرسان فیزیک، پس از متوسطه | مدیران علوم طبیعی | مهندسان مواد | مهندسان هسته‌ای</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Conduct research in physical science specialties not classified separately. | Design and perform experiments to investigate physical and chemical phenomena. | Operate specialized instrumentation to measure physical properties and processes. | Develop mathematical and computational models of physical systems. | Analyze experimental and observational data and quantify measurement uncertainty. | Prepare research reports, technical papers, and proposals for funding. | Interpret findings and advise on their industrial or environmental applications. | Calibrate and maintain scientific equipment and verify instrument performance. | Collect field samples and environmental measurements under varied conditions. | Review scientific literature and evaluate new measurement techniques. | Supervise technicians and coordinate laboratory or field operations. | Ensure compliance with safety procedures for hazardous materials and radiation. | Present technical findings to scientific, regulatory, and management audiences. | Maintain detailed records of methods, calibrations, and results.</t>
+          <t>انجام پژوهش در تخصص‌های علوم فیزیکی که جداگانه طبقه‌بندی نشده‌اند. | طراحی و انجام آزمایش برای بررسی پدیده‌های فیزیکی و شیمیایی. | کار با ابزارهای دقیق تخصصی برای اندازه‌گیری خواص و فرایندهای فیزیکی. | تدوین مدل‌های ریاضی و محاسباتی سامانه‌های فیزیکی. | تجزیه و تحلیل داده‌های آزمایشی و مشاهده‌ای و کمّی‌سازی عدم قطعیت اندازه‌گیری. | تهیه گزارش‌های پژوهشی، مقالات فنی و پیشنهادهای دریافت اعتبار مالی. | تفسیر یافته‌ها و ارائه مشاوره درباره کاربردهای صنعتی یا محیط‌زیستی آن‌ها. | کالیبراسیون و نگهداری تجهیزات علمی و راستی‌آزمایی عملکرد ابزارها. | گردآوری نمونه‌های میدانی و انجام اندازه‌گیری‌های محیط‌زیستی در شرایط گوناگون. | بازبینی ادبیات علمی و ارزیابی فنون اندازه‌گیری جدید. | سرپرستی تکنسین‌ها و هماهنگی عملیات آزمایشگاهی یا میدانی. | حصول اطمینان از رعایت رویه‌های ایمنی مربوط به مواد خطرناک و پرتوها. | ارائه یافته‌های فنی به مخاطبان علمی، نظارتی و مدیریتی. | نگهداری سوابق دقیق روش‌ها، کالیبراسیون‌ها و نتایج.</t>
         </is>
       </c>
     </row>
@@ -835,42 +835,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Remote Sensing Scientists and Technologists (دانشمندان و فناوران سنجش از دور)</t>
+          <t>دانشمندان و فناوران سنجش از دور (Remote Sensing Scientists and Technologists)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Geospatial Intelligence Analyst | Image Scientist | Remote Sensing Analyst | Remote Sensing Scientist | Research Scientist | Scientist | Sensor Specialist</t>
+          <t>تحلیل‌گر اطلاعات مکانی | دانشمند پردازش تصویر | تحلیل‌گر سنجش از دور | دانشمند سنجش از دور | دانشمند پژوهشی | دانشمند | کارشناس حسگر</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>نرم‌افزار Adobe Creative Cloud | نقشه‌های هوانوردی | Agisoft Metashape | Airdata | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | ArduPilot Mission Planner | Atlassian JIRA | BAE Systems SOCET GXP | Bash | C | C# | C++ | نرم‌افزار کالیبراسیون | CloudCompare | Docker | ESRI ArcGIS software | ESRI Site Scan for ArcGIS | Elasticsearch | Epic Systems | زبان نشانه‌گذاری توسعه‌پذیر XML | FLIR Thermal Studio Suite | نرم‌افزار سنجش از دور Gamma | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Git | GitHub | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Go | سیستم کدگذاری رویه‌های مشترک مراقبت‌های بهداشتی HCPCS | Hypertext preprocessor PHP | نرم‌افزار پردازش تصویر | Interface definition language IDL | JavaScript | JavaScript Object Notation JSON | Kitty Hawk | LP360 | سیستم مدیریت یادگیری LMS | Leica Geosystems ERDAS IMAGINE | Linux | Litchi | نرم‌افزار Microsoft Azure | Microsoft Excel | Microsoft Image Composite Editor | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | MySQL | NoSQL | Node.js | Objective C | OpenDroneMap | Oracle Database | Oracle Java | PCI Geomatics Geomatica | Perl | Pix4D Pix4Dmapper | PostgreSQL | Puppet | Python | R | RSI ENVI | Ruby | Ruby on Rails | نرم‌افزار Salesforce | Scala | Selenium | زبان پرس‌وجوی ساختاریافته SQL | Swift | Tableau | The MathWorks MATLAB | UNIX | UgCS | نرم‌افزار مرورگر وب | YouTube</t>
+          <t>نرم‌افزار Adobe Creative Cloud | نقشه‌های هوانوردی | Agisoft Metashape | Airdata | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | ArduPilot Mission Planner | Atlassian JIRA | BAE Systems SOCET GXP | Bash | C | C# | C++ | نرم‌افزار کالیبراسیون | CloudCompare | Docker | نرم‌افزار ESRI ArcGIS | ESRI Site Scan for ArcGIS | Elasticsearch | Epic Systems | زبان نشانه‌گذاری توسعه‌پذیر XML | FLIR Thermal Studio Suite | نرم‌افزار سنجش از دور Gamma | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Git | GitHub | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Go | سیستم کدگذاری رویه‌های رایج مراقبت‌های بهداشتی HCPCS | Hypertext preprocessor PHP | نرم‌افزار پردازش تصویر | زبان تعریف رابط IDL | JavaScript | JavaScript Object Notation JSON | Kitty Hawk | LP360 | سیستم مدیریت یادگیری LMS | Leica Geosystems ERDAS IMAGINE | Linux | Litchi | نرم‌افزار Microsoft Azure | Microsoft Excel | Microsoft Image Composite Editor | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft Visio | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | MySQL | NoSQL | Node.js | Objective C | OpenDroneMap | Oracle Database | Oracle Java | PCI Geomatics Geomatica | Perl | Pix4D Pix4Dmapper | PostgreSQL | Puppet | Python | R | RSI ENVI | Ruby | Ruby on Rails | نرم‌افزار Salesforce | Scala | Selenium | زبان پرس‌وجوی ساختاریافته SQL | Swift | Tableau | The MathWorks MATLAB | UNIX | UgCS | نرم‌افزار مرورگر وب | YouTube</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Critical Thinking | Science | Active Listening | Writing | Speaking | Mathematics | Active Learning | Monitoring | Learning Strategies</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Geography | Computers and Electronics | Mathematics | Engineering and Technology | English Language | Physics | Design | Customer and Personal Service | Administration and Management | Biology</t>
+          <t>جغرافیا | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | فیزیک | طراحی | خدمات مشتری و شخصی | مدیریت و اداره | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inductive Reasoning | Deductive Reasoning | Problem Sensitivity | Near Vision | Oral Comprehension | Written Comprehension | Oral Expression | Written Expression | Information Ordering | Mathematical Reasoning | Category Flexibility | Number Facility | Speech Clarity | Fluency of Ideas | Flexibility of Closure | Speech Recognition | Originality | Visualization | Far Vision | Selective Attention | Perceptual Speed</t>
+          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | اصالت | تجسم | بینایی دور | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>E-Mail | Importance of Being Exact or Accurate | Indoors, Environmentally Controlled | Spend Time Sitting | Telephone Conversations | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Contact With Others</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Aerospace Engineering and Operations Technologists and Technicians | Aerospace Engineers | Atmospheric and Space Scientists | Avionics Technicians | Calibration Technologists and Technicians | Camera Operators, Television, Video, and Film | Cartographers and Photogrammetrists | Electrical and Electronic Engineering Technologists and Technicians | Electrical and Electronics Repairers, Commercial and Industrial Equipment | Electro-Mechanical and Mechatronics Technologists and Technicians | Electronics Engineers, Except Computer | Geodetic Surveyors | Geographic Information Systems Technologists and Technicians | Geological Technicians, Except Hydrologic Technicians | Hydrologic Technicians | Radio Frequency Identification Device Specialists | Remote Sensing Technicians | Robotics Engineers | Robotics Technicians | Surveying and Mapping Technicians</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | دانشمندان علوم جوی و فضایی | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | اپراتورهای دوربین، تلویزیون، ویدئو و فیلم | نقشه‌برداران و فتوگرامتریست‌ها | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | نقشه‌برداران ژئودتیک | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | متخصصان دستگاه‌های شناسایی با فرکانس رادیویی | تکنسین‌های سنجش از دور | مهندسان رباتیک | تکنسین‌های رباتیک | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Analyze data acquired from aircraft, satellites, or ground-based platforms, using statistical analysis software, image analysis software, or Geographic Information Systems (GIS). | Apply remote sensing data or techniques, such as surface water modeling or dust cloud detection, to address environmental issues. | Attend meetings or seminars or read current literature to maintain knowledge of developments in the field of remote sensing. | Collect supporting data, such as climatic or field survey data, to corroborate remote sensing data analyses. | Compile and format image data to increase its usefulness. | Conduct research into the application or enhancement of remote sensing technology. | Design or implement strategies for collection, analysis, or display of geographic data. | Develop automated routines to correct for the presence of image distorting artifacts, such as ground vegetation. | Develop new analytical techniques or sensor systems. | Develop or build databases for remote sensing or related geospatial project information. | Direct all activity associated with implementation, operation, or enhancement of remote sensing hardware or software. | Direct installation or testing of new remote sensing hardware or software. | Discuss project goals, equipment requirements, or methodologies with colleagues or team members. | Integrate other geospatial data sources into projects. | Manage or analyze data obtained from remote sensing systems to obtain meaningful results. | Monitor quality of remote sensing data collection operations to determine if procedural or equipment changes are necessary. | Organize and maintain geospatial data and associated documentation. | Participate in fieldwork. | Prepare or deliver reports or presentations of geospatial project information. | Process aerial or satellite imagery to create products such as land cover maps. | Recommend new remote sensing hardware or software acquisitions. | Set up or maintain remote sensing data collection systems. | Train technicians in the use of remote sensing technology. | Use remote sensing data for forest or carbon tracking activities to assess the impact of environmental change.</t>
+          <t>تجزیه و تحلیل داده‌های به‌دست‌آمده از هواپیما، ماهواره یا سکوهای زمینی، با استفاده از نرم‌افزارهای تحلیل آماری، نرم‌افزارهای تحلیل تصویر یا سامانه‌های اطلاعات جغرافیایی (GIS). | به‌کارگیری داده‌ها یا فنون سنجش از دور، مانند مدل‌سازی آب‌های سطحی یا تشخیص توده‌های گردوغبار، برای رسیدگی به مسائل محیط‌زیستی. | شرکت در نشست‌ها یا سمینارها یا مطالعه ادبیات روز برای به‌روز نگه‌داشتن دانش تحولات حوزه سنجش از دور. | گردآوری داده‌های پشتیبان، مانند داده‌های اقلیمی یا برداشت میدانی، برای تأیید تحلیل‌های داده سنجش از دور. | گردآوری و قالب‌بندی داده‌های تصویری برای افزایش کارایی آن‌ها. | انجام پژوهش درباره کاربرد یا ارتقای فناوری سنجش از دور. | طراحی یا اجرای راهبردهای گردآوری، تجزیه و تحلیل یا نمایش داده‌های جغرافیایی. | تدوین روال‌های خودکار برای تصحیح آثار اعوجاج‌زا در تصویر، مانند پوشش گیاهی سطح زمین. | توسعه فنون تحلیلی یا سامانه‌های حسگر جدید. | تدوین یا ساخت پایگاه‌های داده برای اطلاعات پروژه‌های سنجش از دور یا پروژه‌های مکانی مرتبط. | هدایت همه فعالیت‌های مرتبط با استقرار، بهره‌برداری یا ارتقای سخت‌افزار و نرم‌افزار سنجش از دور. | هدایت نصب یا آزمون سخت‌افزار یا نرم‌افزار جدید سنجش از دور. | بحث درباره اهداف پروژه، الزامات تجهیزاتی یا روش‌شناسی با همکاران یا اعضای تیم. | یکپارچه‌سازی سایر منابع داده مکانی در پروژه‌ها. | مدیریت یا تجزیه و تحلیل داده‌های به‌دست‌آمده از سامانه‌های سنجش از دور برای دستیابی به نتایج معنادار. | پایش کیفیت عملیات گردآوری داده سنجش از دور برای تعیین لزوم تغییر در رویه‌ها یا تجهیزات. | سازماندهی و نگهداری داده‌های مکانی و مستندات مرتبط با آن‌ها. | مشارکت در کار میدانی. | تهیه یا ارائه گزارش‌ها یا ارائه‌های اطلاعات پروژه‌های مکانی. | پردازش تصاویر هوایی یا ماهواره‌ای برای تولید محصولاتی مانند نقشه‌های پوشش زمین. | پیشنهاد تهیه سخت‌افزار یا نرم‌افزار جدید سنجش از دور. | راه‌اندازی یا نگهداری سامانه‌های گردآوری داده سنجش از دور. | آموزش تکنسین‌ها در زمینه استفاده از فناوری سنجش از دور. | استفاده از داده‌های سنجش از دور در فعالیت‌های پایش جنگل یا کربن برای ارزیابی اثر تغییرات محیط‌زیستی.</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Economists (اقتصاددانان)</t>
+          <t>اقتصاددانان (Economists)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Economic Advisor | Economic Analyst | Economic Consultant | Economic Development Specialist | Economist | Forensic Economist | Project Economist | Research Economist | Revenue Research Analyst | Tax Economist</t>
+          <t>مشاور اقتصادی | تحلیل‌گر اقتصادی | مشاور اقتصادی | کارشناس توسعه اقتصادی | اقتصاددان | اقتصاددان قضایی | اقتصاددان پروژه | اقتصاددان پژوهشی | تحلیل‌گر پژوهش درآمد | اقتصاددان مالیاتی</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Reading Comprehension | Mathematics | Critical Thinking | Speaking | Writing | Active Listening | Active Learning | Monitoring | Learning Strategies</t>
+          <t>درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mathematics | Economics and Accounting | English Language | Computers and Electronics | Education and Training</t>
+          <t>ریاضیات | اقتصاد و حسابداری | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Written Comprehension | Inductive Reasoning | Mathematical Reasoning | Written Expression | Deductive Reasoning | Speech Clarity | Oral Comprehension | Oral Expression | Fluency of Ideas | Problem Sensitivity | Speech Recognition | Near Vision | Number Facility | Information Ordering | Originality | Category Flexibility</t>
+          <t>درک کتبی | استدلال استقرایی | استدلال ریاضی | بیان کتبی | استدلال قیاسی | وضوح گفتار | درک شفاهی | بیان شفاهی | روانی ایده‌ها | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | توانایی عددی | ترتیب‌دهی اطلاعات | اصالت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>E-Mail | Spend Time Sitting | Freedom to Make Decisions | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Indoors, Environmentally Controlled | Determine Tasks, Priorities and Goals | Importance of Being Exact or Accurate | Level of Competition | Written Letters and Memos | Work With or Contribute to a Work Group or Team | Time Pressure | Frequency of Decision Making | Contact With Others</t>
+          <t>ایمیل | صرف زمان برای نشستن | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | سطح رقابت | نامه‌ها و یادداشت‌های کتبی | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | فراوانی تصمیم‌گیری | ارتباط با دیگران</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Actuaries | Business Intelligence Analysts | Business Teachers, Postsecondary | Climate Change Policy Analysts | Data Scientists | Economics Teachers, Postsecondary | Environmental Economists | Financial Quantitative Analysts | Financial Risk Specialists | Financial and Investment Analysts | Investment Fund Managers | Market Research Analysts and Marketing Specialists | Operations Research Analysts | Personal Financial Advisors | Political Science Teachers, Postsecondary | Political Scientists | Securities, Commodities, and Financial Services Sales Agents | Social Science Research Assistants | Sociologists | Statisticians</t>
+          <t>کارشناسان آمار بیمه (اکچوئری) | تحلیلگران هوش تجاری | اساتید کسب‌وکار، پس از متوسطه | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان داده | استادان اقتصاد، پس از متوسطه | اقتصاددانان محیط‌زیست | تحلیلگران کمی مالی | متخصصان ریسک مالی | تحلیلگران مالی و سرمایه‌گذاری | مدیران صندوق سرمایه‌گذاری | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | تحلیل‌گران تحقیق در عملیات | مشاوران مالی شخصی | استادان علوم سیاسی، پس از متوسطه | دانشمندان علوم سیاسی | نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران تحقیقات علوم اجتماعی | جامعه‌شناسان | آمارشناسان</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Compile, analyze, and report data to explain economic phenomena and forecast market trends, applying mathematical models and statistical techniques. | Conduct research on economic issues, and disseminate research findings through technical reports or scientific articles in journals. | Develop economic guidelines and standards, and prepare points of view used in forecasting trends and formulating economic policy. | Explain economic impact of policies to the public. | Forecast production and consumption of renewable resources and supply, consumption, and depletion of non-renewable resources. | Formulate recommendations, policies, or plans to solve economic problems or to interpret markets. | Provide advice and consultation on economic relationships to businesses, public and private agencies, and other employers. | Provide litigation support, such as writing reports for expert testimony or testifying as an expert witness. | Review documents written by others. | Study economic and statistical data in area of specialization, such as finance, labor, or agriculture. | Study the socioeconomic impacts of new public policies, such as proposed legislation, taxes, services, and regulations. | Supervise research projects and students' study projects. | Teach theories, principles, and methods of economics. | Testify at regulatory or legislative hearings concerning the estimated effects of changes in legislation or public policy, and present recommendations based on cost-benefit analyses.</t>
+          <t>گردآوری، تجزیه و تحلیل و گزارش داده‌ها برای تبیین پدیده‌های اقتصادی و پیش‌بینی روندهای بازار، با به‌کارگیری مدل‌های ریاضی و فنون آماری. | انجام پژوهش درباره مسائل اقتصادی و انتشار یافته‌های پژوهشی از راه گزارش‌های فنی یا مقالات علمی در نشریات. | تدوین دستورالعمل‌ها و استانداردهای اقتصادی و تهیه دیدگاه‌های مورد استفاده در پیش‌بینی روندها و تدوین سیاست اقتصادی. | تبیین اثر اقتصادی سیاست‌ها برای عموم مردم. | پیش‌بینی تولید و مصرف منابع تجدیدپذیر و عرضه، مصرف و تحلیل‌رفتن منابع تجدیدناپذیر. | تدوین توصیه‌ها، سیاست‌ها یا برنامه‌هایی برای حل مسائل اقتصادی یا تفسیر بازارها. | ارائه مشاوره و خدمات مشورتی درباره روابط اقتصادی به کسب‌وکارها، نهادهای دولتی و خصوصی و سایر کارفرمایان. | ارائه پشتیبانی در دعاوی حقوقی، مانند نگارش گزارش برای شهادت کارشناسی یا حضور به‌عنوان شاهد کارشناس. | بازبینی اسناد نگاشته‌شده به‌دست دیگران. | مطالعه داده‌های اقتصادی و آماری در حوزه تخصصی، مانند مالیه، کار یا کشاورزی. | مطالعه پیامدهای اجتماعی‌اقتصادی سیاست‌های عمومی جدید، مانند لوایح پیشنهادی، مالیات‌ها، خدمات و مقررات. | سرپرستی پروژه‌های پژوهشی و پروژه‌های مطالعاتی دانشجویان. | تدریس نظریه‌ها، اصول و روش‌های اقتصاد. | ادای شهادت در جلسات استماع نظارتی یا قانون‌گذاری درباره آثار برآوردی تغییرات قانون یا سیاست عمومی و ارائه توصیه بر پایه تحلیل هزینه‌فایده.</t>
         </is>
       </c>
     </row>
@@ -949,42 +949,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Environmental Economists (اقتصاددانان محیط‌زیست)</t>
+          <t>اقتصاددانان محیط‌زیست (Environmental Economists)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Environmental Economist | Natural Resource Economist | Research Economist | Resource Economist</t>
+          <t>اقتصاددان محیط‌زیست | اقتصاددان منابع طبیعی | اقتصاددان پژوهشی | اقتصاددان منابع</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Aptech Systems GAUSS | C | C# | C++ | Camfit Data Limited Microfit | ESRI ArcGIS software | Econometric Software LIMDEP | Estima Regression Analysis of Time Series RATS | Formula translation/translator FORTRAN | General algebraic modeling system GAMS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Global Insight AREMOS | IBM SPSS Statistics | Insightful S-PLUS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Word | Minitab | MySQL | Python | Quantitative Micro Software EViews | SAS | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Tableau | The MathWorks MATLAB | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
+          <t>Aptech Systems GAUSS | C | C# | C++ | Camfit Data Limited Microfit | نرم‌افزار ESRI ArcGIS | Econometric Software LIMDEP | Estima Regression Analysis of Time Series RATS | Formula translation/translator FORTRAN | General algebraic modeling system GAMS | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Global Insight AREMOS | IBM SPSS Statistics | Insightful S-PLUS | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Word | Minitab | MySQL | Python | Quantitative Micro Software EViews | SAS | StataCorp Stata | زبان پرس‌وجوی ساختاریافته SQL | Tableau | The MathWorks MATLAB | نرم‌افزار مرورگر وب | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Writing | Active Listening | Reading Comprehension | Critical Thinking | Mathematics | Active Learning | Speaking | Monitoring | Learning Strategies</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | سخن گفتن | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mathematics | Economics and Accounting | English Language | Computers and Electronics | Education and Training | Law and Government</t>
+          <t>ریاضیات | اقتصاد و حسابداری | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Written Comprehension | Mathematical Reasoning | Oral Comprehension | Oral Expression | Written Expression | Number Facility | Speech Clarity | Problem Sensitivity | Deductive Reasoning | Inductive Reasoning | Near Vision | Speech Recognition | Fluency of Ideas | Originality | Information Ordering | Category Flexibility | Selective Attention | Flexibility of Closure | Memorization</t>
+          <t>درک کتبی | استدلال ریاضی | درک شفاهی | بیان شفاهی | بیان کتبی | توانایی عددی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>E-Mail | Determine Tasks, Priorities and Goals | Freedom to Make Decisions | Indoors, Environmentally Controlled | Spend Time Sitting | Face-to-Face Discussions with Individuals and Within Teams | Importance of Being Exact or Accurate | Level of Competition | Telephone Conversations</t>
+          <t>ایمیل | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | سطح رقابت | مکالمات تلفنی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Biologists | Chief Sustainability Officers | Climate Change Policy Analysts | Conservation Scientists | Data Scientists | Economics Teachers, Postsecondary | Economists | Environmental Restoration Planners | Environmental Scientists and Specialists, Including Health | Financial Quantitative Analysts | Financial Risk Specialists | Geoscientists, Except Hydrologists and Geographers | Hydrologists | Industrial Ecologists | Political Scientists | Sociologists | Soil and Plant Scientists | Statisticians | Sustainability Specialists | Zoologists and Wildlife Biologists</t>
+          <t>زیست‌شناسان | مدیران ارشد پایداری | تحلیل‌گران سیاست تغییرات اقلیمی | دانشمندان حفاظت | دانشمندان داده | استادان اقتصاد، پس از متوسطه | اقتصاددانان | برنامه‌ریزان احیای محیط‌زیست | دانشمندان و متخصصان محیط زیست، شامل بهداشت | تحلیلگران کمی مالی | متخصصان ریسک مالی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | آب‌شناسان | بوم‌شناسان صنعتی | دانشمندان علوم سیاسی | جامعه‌شناسان | دانشمندان خاک و گیاه | آمارشناسان | متخصصان پایداری | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Assess the costs and benefits of various activities, policies, or regulations that affect the environment or natural resource stocks. | Collect and analyze data to compare the environmental implications of economic policy or practice alternatives. | Conduct research on economic and environmental topics, such as alternative fuel use, public and private land use, soil conservation, air and water pollution control, and endangered species protection. | Conduct research to study the relationships among environmental problems and patterns of economic production and consumption. | Demonstrate or promote the economic benefits of sound environmental regulations. | Develop economic models, forecasts, or scenarios to predict future economic and environmental outcomes. | Develop environmental research project plans, including information on budgets, goals, deliverables, timelines, and resource requirements. | Develop programs or policy recommendations to achieve environmental goals in cost-effective ways. | Develop programs or policy recommendations to promote sustainability and sustainable development. | Develop systems for collecting, analyzing, and interpreting environmental and economic data. | Examine the exhaustibility of natural resources or the long-term costs of environmental rehabilitation. | Identify and recommend environmentally friendly business practices. | Interpret indicators to ascertain the overall health of an environment. | Monitor or analyze market and environmental trends. | Perform complex, dynamic, and integrated mathematical modeling of ecological, environmental, or economic systems. | Prepare and deliver presentations to communicate economic and environmental study results, to present policy recommendations, or to raise awareness of environmental consequences. | Teach courses in environmental economics. | Write research proposals and grant applications to obtain private or public funding for environmental and economic studies. | Write social, legal, or economic impact statements to inform decision makers for natural resource policies, standards, or programs. | Write technical documents or academic articles to communicate study results or economic forecasts.</t>
+          <t>ارزیابی هزینه‌ها و منافع فعالیت‌ها، سیاست‌ها یا مقررات گوناگونی که بر محیط‌زیست یا ذخایر منابع طبیعی اثر می‌گذارند. | گردآوری و تجزیه و تحلیل داده‌ها برای مقایسه پیامدهای محیط‌زیستی گزینه‌های سیاستی یا اجرایی اقتصادی. | انجام پژوهش در موضوعات اقتصادی و محیط‌زیستی، مانند استفاده از سوخت‌های جایگزین، کاربری اراضی عمومی و خصوصی، حفاظت خاک، کنترل آلودگی هوا و آب، و حفاظت از گونه‌های در معرض خطر. | انجام پژوهش برای مطالعه روابط میان مسائل محیط‌زیستی و الگوهای تولید و مصرف اقتصادی. | نشان دادن یا ترویج منافع اقتصادی مقررات محیط‌زیستی درست. | تدوین مدل‌ها، پیش‌بینی‌ها یا سناریوهای اقتصادی برای پیش‌بینی پیامدهای اقتصادی و محیط‌زیستی آینده. | تدوین برنامه‌های پروژه‌های پژوهشی محیط‌زیستی، شامل اطلاعات بودجه، اهداف، خروجی‌ها، زمان‌بندی و الزامات منابع. | تدوین برنامه‌ها یا توصیه‌های سیاستی برای دستیابی به اهداف محیط‌زیستی به شیوه‌های مقرون‌به‌صرفه. | تدوین برنامه‌ها یا توصیه‌های سیاستی برای ترویج پایداری و توسعه پایدار. | تدوین سامانه‌هایی برای گردآوری، تجزیه و تحلیل و تفسیر داده‌های محیط‌زیستی و اقتصادی. | بررسی پایان‌پذیری منابع طبیعی یا هزینه‌های بلندمدت بازسازی محیط‌زیست. | شناسایی و پیشنهاد شیوه‌های کسب‌وکار سازگار با محیط‌زیست. | تفسیر شاخص‌ها برای تشخیص سلامت کلی یک محیط. | پایش یا تجزیه و تحلیل روندهای بازار و محیط‌زیست. | انجام مدل‌سازی ریاضی پیچیده، پویا و یکپارچه سامانه‌های بوم‌شناختی، محیط‌زیستی یا اقتصادی. | تهیه و ارائه ارائه‌هایی برای انتقال نتایج مطالعات اقتصادی و محیط‌زیستی، طرح توصیه‌های سیاستی یا افزایش آگاهی از پیامدهای محیط‌زیستی. | تدریس دروس اقتصاد محیط‌زیست. | نگارش پیشنهادهای پژوهشی و درخواست‌های اعطای اعتبار برای دریافت تأمین مالی خصوصی یا عمومی مطالعات محیط‌زیستی و اقتصادی. | نگارش بیانیه‌های اثر اجتماعی، حقوقی یا اقتصادی برای آگاهی‌بخشی به تصمیم‌گیران درباره سیاست‌ها، استانداردها یا برنامه‌های منابع طبیعی. | نگارش اسناد فنی یا مقالات علمی برای انتقال نتایج مطالعات یا پیش‌بینی‌های اقتصادی.</t>
         </is>
       </c>
     </row>
@@ -1006,12 +1006,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Survey Researchers (پژوهشگران نظرسنجی)</t>
+          <t>پژوهشگران نظرسنجی (Survey Researchers)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Data Analyst | Market Survey Representative | Research Associate | Research Fellow | Research Interviewer | Research Scientist | Survey Methodologist | Survey Researcher | Survey Statistician | Telephone Interviewer</t>
+          <t>تحلیل‌گر داده | نماینده نظرسنجی بازار | دستیار پژوهشی | همکار پژوهشی | مصاحبه‌کننده پژوهشی | دانشمند پژوهشی | روش‌شناس نظرسنجی | پژوهشگر نظرسنجی | آماردان نظرسنجی | مصاحبه‌کننده تلفنی</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1021,27 +1021,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Speaking | Critical Thinking | Writing | Active Listening | Reading Comprehension | Mathematics | Active Learning | Learning Strategies | Monitoring</t>
+          <t>سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>English Language | Sociology and Anthropology | Mathematics | Computers and Electronics | Administration and Management | Customer and Personal Service | Psychology | Administrative | Communications and Media | Education and Training</t>
+          <t>زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | روان‌شناسی | اداری | ارتباطات و رسانه | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Inductive Reasoning | Written Expression | Written Comprehension | Oral Comprehension | Oral Expression | Deductive Reasoning | Information Ordering | Mathematical Reasoning | Near Vision | Speech Clarity | Number Facility | Speech Recognition | Category Flexibility | Problem Sensitivity | Fluency of Ideas | Flexibility of Closure | Originality | Selective Attention</t>
+          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی | بینایی نزدیک | وضوح گفتار | توانایی عددی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>E-Mail | Indoors, Environmentally Controlled | Importance of Being Exact or Accurate | Spend Time Sitting | Work With or Contribute to a Work Group or Team | Face-to-Face Discussions with Individuals and Within Teams | Telephone Conversations | Freedom to Make Decisions | Determine Tasks, Priorities and Goals | Deal With External Customers or the Public in General | Time Pressure | Contact With Others | Coordinate or Lead Others in Accomplishing Work Activities | Work Outcomes and Results of Other Workers | Impact of Decisions on Co-workers or Company Results</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | تعامل با مشتریان خارجی یا عموم مردم | فشار زمانی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Biostatisticians | Business Intelligence Analysts | Clinical Data Managers | Clinical Research Coordinators | Data Scientists | Eligibility Interviewers, Government Programs | Financial Quantitative Analysts | Geodetic Surveyors | Health Information Technologists and Medical Registrars | Industrial-Organizational Psychologists | Instructional Coordinators | Intelligence Analysts | Interviewers, Except Eligibility and Loan | Management Analysts | Market Research Analysts and Marketing Specialists | Operations Research Analysts | Social Science Research Assistants | Sociologists | Statistical Assistants | Statisticians</t>
+          <t>آمارشناسان زیستی | تحلیلگران هوش تجاری | مدیران داده‌های بالینی | هماهنگ‌کنندگان تحقیقات بالینی | دانشمندان داده | مصاحبه‌کنندگان واجد شرایط بودن، برنامه‌های دولتی | تحلیلگران کمی مالی | نقشه‌برداران ژئودتیک | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | روان‌شناسان صنعتی-سازمانی | هماهنگ‌کنندگان آموزشی | تحلیلگران اطلاعاتی | مصاحبه‌کنندگان، به جز واجدین شرایط و وام | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | تحلیل‌گران تحقیق در عملیات | دستیاران تحقیقات علوم اجتماعی | جامعه‌شناسان | دستیاران آماری | آمارشناسان</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Analyze data from surveys, old records, or case studies, using statistical software. | Collaborate with other researchers in the planning, implementation, and evaluation of surveys. | Conduct research to gather information about survey topics. | Conduct surveys and collect data, using methods such as interviews, questionnaires, focus groups, market analysis surveys, public opinion polls, literature reviews, and file reviews. | Consult with clients to identify survey needs and specific requirements, such as special samples. | Determine and specify details of survey projects, including sources of information, procedures to be used, and the design of survey instruments and materials. | Direct and review the work of staff members, including survey support staff and interviewers who gather survey data. | Direct updates and changes in survey implementation and methods. | Hire and train recruiters and data collectors. | Monitor and evaluate survey progress and performance, using sample disposition reports and response rate calculations. | Prepare and present summaries and analyses of survey data, including tables, graphs, and fact sheets that describe survey techniques and results. | Produce documentation of the questionnaire development process, data collection methods, sampling designs, and decisions related to sample statistical weighting. | Review, classify, and record survey data in preparation for computer analysis. | Support, plan, and coordinate operations for single or multiple surveys. | Write proposals to win new projects. | Write training manuals to be used by survey interviewers.</t>
+          <t>تجزیه و تحلیل داده‌های حاصل از نظرسنجی‌ها، سوابق پیشین یا مطالعات موردی، با استفاده از نرم‌افزارهای آماری. | همکاری با سایر پژوهشگران در برنامه‌ریزی، اجرا و ارزیابی نظرسنجی‌ها. | انجام پژوهش برای گردآوری اطلاعات درباره موضوعات نظرسنجی. | اجرای نظرسنجی و گردآوری داده، با روش‌هایی مانند مصاحبه، پرسش‌نامه، گروه کانونی، نظرسنجی تحلیل بازار، نظرسنجی افکار عمومی، مرور ادبیات و بررسی پرونده‌ها. | رایزنی با کارفرمایان برای شناسایی نیازهای نظرسنجی و الزامات خاص، مانند نمونه‌های ویژه. | تعیین و تصریح جزئیات پروژه‌های نظرسنجی، شامل منابع اطلاعات، رویه‌های مورد استفاده و طراحی ابزارها و مواد نظرسنجی. | هدایت و بازبینی کار کارکنان، از جمله کارکنان پشتیبانی نظرسنجی و مصاحبه‌گرانی که داده‌ها را گردآوری می‌کنند. | هدایت به‌روزرسانی‌ها و تغییرات در اجرا و روش‌های نظرسنجی. | استخدام و آموزش جذب‌کنندگان و گردآورندگان داده. | پایش و ارزیابی پیشرفت و عملکرد نظرسنجی، با استفاده از گزارش‌های وضعیت نمونه و محاسبه نرخ پاسخ‌گویی. | تهیه و ارائه خلاصه‌ها و تحلیل‌های داده‌های نظرسنجی، شامل جدول‌ها، نمودارها و برگه‌های اطلاعاتی که فنون و نتایج نظرسنجی را تشریح می‌کنند. | تولید مستندات فرایند تدوین پرسش‌نامه، روش‌های گردآوری داده، طرح‌های نمونه‌گیری و تصمیم‌های مربوط به وزن‌دهی آماری نمونه. | بازبینی، طبقه‌بندی و ثبت داده‌های نظرسنجی برای آماده‌سازی تحلیل رایانه‌ای. | پشتیبانی، برنامه‌ریزی و هماهنگی عملیات یک یا چند نظرسنجی. | نگارش پیشنهادها برای کسب پروژه‌های جدید. | نگارش راهنماهای آموزشی برای استفاده مصاحبه‌گران نظرسنجی.</t>
         </is>
       </c>
     </row>

--- a/data_extactor/batch_10_fa/batch_0024_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0024_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | زبان انگلیسی | ریاضیات</t>
+          <t>قانون و دولت | زبان انگلیسی | ریاضیات</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در نتیجه‌گیری | انعطاف‌پذیری طبقه‌بندی | ابتکار | روانی ایده‌ها | استدلال ریاضی | توجه انتخابی | محاسبات عددی</t>
+          <t>درک کتبی | درک شفاهی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | استدلال ریاضی | توجه انتخابی | توانایی عددی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>دانشمندان علوم جوی و فضایی | متخصصان و مدیران احیای اراضی صنعتی متروکه | مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان | بازرسان انطباق زیست‌محیطی | اقتصاددانان محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | استادان علوم زیست‌محیطی دانشگاه | دانشمندان و متخصصان محیط زیست و بهداشت | متخصصان مدیریت ریسک مالی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های هیدرولوژی و آب‌شناسی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | متخصصان علوم سیاسی | متخصصان پایداری زیست‌محیطی | برنامه‌ریزان شهری و منطقه‌ای | متخصصان منابع آب</t>
+          <t>دانشمندان و کارشناسان علوم جوی و فضا | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان | بازرسان رعایت ضوابط زیست‌محیطی | اقتصاددانان محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | استادان و مدرسان علوم محیط‌زیست در دانشگاه‌ها و مراکز آموزش عالی | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کارشناسان ریسک مالی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | دانشمندان و پژوهشگران علوم سیاسی | کارشناسان پایداری و توسعه پایدار | برنامه‌ریزان شهری و منطقه‌ای | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>تحلیل و تلخیص یافته‌های پژوهشی اقلیمی جهت اطلاع‌رسانی به قانون‌گذاران، نهادهای نظارتی و سایر ذی‌نفعان | تدوین و مشارکت در اجرای برنامه‌های آموزشی و ترویجی در زمینه محیط زیست و تغییر اقلیم | جمع‌آوری و ارزیابی پژوهش‌های مرتبط با تغییر اقلیم از سازمان‌های دولتی و مراکز پژوهشی | تدوین توصیه‌های سیاستی و تقنینی بر اساس اصول، مبانی و فرآیندهای مدیریت تغییر اقلیم | تهیه گزارش‌های پژوهشی، یادداشت‌های سیاستی و خلاصه‌های مدیریتی برای سازمان‌های دولتی و تشکل‌های زیست‌محیطی | ارائه و دفاع از طرح‌های پیشنهادی پژوهشی در حوزه تغییر اقلیم | ارائه مستندات و اطلاعات سیاستی در نشست‌های تخصصی، مراجع دولتی و مجامع عمومی | پیشنهاد سیاست‌های نوآورانه یا بازنگری‌شده در زمینه سوخت‌های فسیلی و پاک، حمل‌ونقل کالا و متغیرهای اقلیمی | ارائه تحلیل‌های تخصصی برای حمایت از خط‌مشی‌های حوزه انرژی‌های تجدیدپذیر، بهره‌وری انرژی و اقلیم | بررسی قوانین و خط‌مشی‌های جاری به‌منظور شناسایی پیامدهای زیست‌محیطی آن‌ها</t>
+          <t>تجزیه و تحلیل و تلخیص یافته‌های پژوهشی مرتبط با اقلیم برای آگاهی‌بخشی به قانون‌گذاران، نهادهای نظارتی یا سایر ذی‌نفعان. | تدوین برنامه‌های آموزشی یا ترویجی در زمینه محیط‌زیست یا تغییر اقلیم، یا مشارکت در تدوین آن‌ها. | گردآوری و بازبینی مطالعات مرتبط با اقلیم از نهادهای دولتی، آزمایشگاه‌های پژوهشی و سایر سازمان‌ها. | ارائه پیشنهادهای قانون‌گذاری مرتبط با تغییر اقلیم یا مدیریت محیط‌زیست، بر پایه سیاست‌ها، اصول، برنامه‌ها، شیوه‌ها و فرایندهای تغییر اقلیم. | تهیه درخواست‌های اعطای اعتبار برای تأمین مالی برنامه‌های مرتبط با تغییر اقلیم، مدیریت محیط‌زیست یا پایداری. | تهیه گزارش‌های مطالعاتی، یادداشت‌ها، خلاصه‌ها، شهادت‌ها یا سایر مواد مکتوب برای آگاهی‌بخشی به نهادهای دولتی یا گروه‌های محیط‌زیستی درباره مسائل محیط‌زیستی، مانند تغییر اقلیم. | ارائه و دفاع از پیشنهادهای پروژه‌های پژوهشی تغییر اقلیم. | ارائه اطلاعات مرتبط با اقلیم در نشست‌های عمومی، دولتی یا سایر نشست‌ها. | ترویج ابتکارهای کاهش تغییر اقلیم نزد نهادهای دولتی یا گروه‌های محیط‌زیستی. | پیشنهاد سیاست‌های جدید یا اصلاح‌شده درباره استفاده از سوخت‌های سنتی و جایگزین، حمل‌ونقل کالا و سایر عوامل مرتبط با اقلیم و تغییر اقلیم. | ارائه پشتیبانی تحلیلی برای خلاصه‌های سیاستی مرتبط با انرژی تجدیدپذیر، بهره‌وری انرژی یا تغییر اقلیم. | پژوهش درباره سیاست‌ها، شیوه‌ها یا رویه‌های مدیریت اقلیم یا محیط‌زیست. | بازبینی سیاست‌ها یا قوانین موجود برای شناسایی پیامدهای محیط‌زیستی آن‌ها. | نگارش گزارش‌ها یا مقالات علمی برای انتقال یافته‌های مطالعات مرتبط با اقلیم.</t>
         </is>
       </c>
     </row>
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | نظارت | علوم پایه | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | نظارت | علوم | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | زبان انگلیسی | جغرافیا | طراحی | ریاضیات | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | حقوق و مقررات دولتی | مهندسی و فناوری | رایانه و الکترونیک | ساختمان و سازه</t>
+          <t>زیست‌شناسی | زبان انگلیسی | جغرافیا | طراحی | ریاضیات | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | مهندسی و فناوری | رایانه و الکترونیک | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | دید نزدیک | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها | محاسبات عددی | دید دور | ابتکار | تجسم فضایی | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بینایی نزدیک | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | توانایی عددی | بینایی دور | اصالت | تجسم | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>زیست‌شناسان | متخصصان و مدیران احیای اراضی صنعتی متروکه | مدیران ارشد پایداری سازمانی | مهندسان عمران | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست و بهداشت | دانشمندان و متخصصان محیط زیست و بهداشت | تکنسین‌های جنگل‌داری و حفاظت | کارشناسان جنگل‌داری | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های هیدرولوژی و آب‌شناسی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مرتع‌داران | دانشمندان علوم خاک و گیاه‌شناسی | متخصصان منابع آب | مهندسان آب و فاضلاب | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>زیست‌شناسان | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | مهندسان عمران | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>پیگیری و اخذ مجوزهای قانونی لازم برای اجرای پروژه‌های بهسازی و احیای زیست‌محیطی | جمع‌آوری و تحلیل داده‌ها به‌منظور تعیین وضعیت زیست‌محیطی و نیازهای احیا | انجام ارزیابی‌های اثرات زیست‌محیطی جهت بررسی پیامدهای بوم‌شناختی آلاینده‌ها، فعالیت‌های انسانی و تغییر اقلیم | تهیه مطالعات امکان‌سنجی فنی و ارزیابی اقتصادی پروژه‌های احیای محیط زیست | ارزیابی میدانی سایت‌ها جهت تعیین میزان خسارات و الزامات بهسازی زیستگاه‌ها | مدل‌سازی و شبیه‌سازی زیست‌محیطی با بهره‌گیری از سامانه‌های اطلاعات جغرافیایی GIS | تدوین برنامه‌های جامع مدیریت و احیای زیستگاه‌ها نظیر احیای پوشش گیاهی بومی و مهار گونه‌های مهاجم | تعیین و تدوین راهکارهای جایگزین جبران و کاهش اثرات زیست‌محیطی مطابق مقررات جاری | بازرسی از کارگاه‌های بهسازی زیست‌محیطی جهت حصول اطمینان از انطباق با استانداردهای ایمنی و محیط زیست | برنامه‌ریزی زمان‌بندی و برآورد بودجه پروژه‌های احیای زیست‌محیطی</t>
+          <t>درخواست مجوزهای لازم برای اجرای پروژه‌های پاک‌سازی محیط‌زیستی. | گردآوری و تجزیه و تحلیل داده‌ها برای تعیین شرایط محیط‌زیستی و نیازهای احیا. | انتقال یافته‌های مطالعات محیط‌زیستی یا پیشنهادهای پاک‌سازی محیط‌زیستی به سایر متخصصان احیا. | انجام مطالعات ارزیابی اثرات محیط‌زیستی برای بررسی آثار بوم‌شناختی آلاینده‌ها، بیماری، فعالیت‌های انسانی، طبیعت و تغییر اقلیم. | انجام مطالعات امکان‌سنجی و هزینه‌فایده برای پروژه‌های پاک‌سازی محیط‌زیستی. | انجام ارزیابی‌های سایت برای تأیید یک زیستگاه یا تعیین آسیب محیط‌زیستی و نیازهای احیا. | ترسیم نمودار برای انتقال برنامه‌ریزی پاک‌سازی محیط‌زیستی، با استفاده از سامانه اطلاعات جغرافیایی (GIS)، طراحی به کمک رایانه (CAD) یا سایر نرم‌افزارهای نقشه‌کشی و نمودارسازی. | ساخت مدل‌ها یا شبیه‌سازی‌های محیط‌زیستی، با استفاده از داده‌های سامانه اطلاعات جغرافیایی (GIS) و دانش بوم‌سازگان‌ها یا مناطق بوم‌شناختی خاص. | تدوین برنامه‌های مدیریت یا احیای زیستگاه، مانند احیای درختان بومی و کنترل علف‌های هرز. | تدوین و ابلاغ توصیه‌ها به مالکان زمین برای حفظ یا احیای شرایط محیط‌زیستی. | تدوین برنامه‌های مدیریت یا احیای محیط‌زیست برای محل‌های دارای خطوط انتقال برق، خطوط لوله گاز طبیعی، پالایشگاه سوخت، نیروگاه زمین‌گرمایی، مزرعه بادی یا مزرعه خورشیدی. | تدوین زمان‌بندی و بودجه پروژه‌های احیای محیط‌زیست. | تدوین برنامه‌های مدیریت منابع طبیعی، با به‌کارگیری دانش برنامه‌ریزی محیط‌زیستی یا الزامات نظارتی محیط‌زیستی ایالتی و فدرال. | شناسایی گزینه‌های جایگزین برای کاهش اثرات محیط‌زیستی، با اطمینان از رعایت استانداردها، قوانین یا مقررات مربوطه. | شناسایی اثرات کوتاه‌مدت و بلندمدت فعالیت‌های پاک‌سازی محیط‌زیستی. | بازرسی محل‌های فعال پاک‌سازی برای اطمینان از رعایت سیاست‌ها، استانداردها یا مقررات محیط‌زیستی و ایمنی. | اطلاع‌رسانی به نهادهای نظارتی یا صادرکننده مجوز درباره انحراف از برنامه‌های پاک‌سازی اجراشده. | برنامه‌ریزی پروژه‌های احیای محیط‌زیست، با استفاده از پایگاه‌های داده زیستی، راهبردهای محیط‌زیستی و نرم‌افزارهای برنامه‌ریزی. | برنامه‌ریزی یا سرپرستی مطالعات محیط‌زیستی برای دستیابی به انطباق با مقررات محیط‌زیستی در ساخت، اصلاح، بهره‌برداری، تملک یا واگذاری تأسیساتی مانند نیروگاه‌ها. | ارائه راهبری فنی در زمینه برنامه‌ریزی محیط‌زیستی به مهندسان انرژی، زیست‌شناسان، زمین‌شناسان یا سایر متخصصانی که برنامه‌ها یا راهبردهای احیا را تدوین می‌کنند. | بازبینی طرح‌های موجود پاک‌سازی محیط‌زیستی. | سرپرستی و ارائه راهنمایی فنی، آموزش یا کمک به کارکنان میدانی که در احیای زیستگاه‌ها فعالیت می‌کنند. | نگارش درخواست‌های اعطای اعتبار برای تأمین مالی پروژه‌های احیا.</t>
         </is>
       </c>
     </row>
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | نگارش | شنیدن فعال | تفکر انتقادی | علوم پایه | یادگیری فعال | ریاضیات | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | سخن گفتن | نگارش | گوش دادن فعال | تفکر انتقادی | علوم | یادگیری فعال | ریاضیات | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | استدلال استقرایی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | استدلال ریاضی | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | ابتکار | روانی ایده‌ها | انعطاف‌پذیری در نتیجه‌گیری | محاسبات عددی | دید دور</t>
+          <t>استدلال قیاسی | استدلال استقرایی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | استدلال ریاضی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | انعطاف‌پذیری بستار | توانایی عددی | بینایی دور</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان کشاورزی | مدیران توسعه فناوری و محصولات سوخت‌های زیستی | متخصصان و مدیران احیای اراضی صنعتی متروکه | مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان محیط زیست | تکنسین‌ها و کاردان‌های فنی مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست و بهداشت | دانشمندان و متخصصان محیط زیست و بهداشت | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های هیدرولوژی و آب‌شناسی | آب‌شناسان و هیدرولوژیست‌ها | مرتع‌داران | دانشمندان علوم خاک و گیاه‌شناسی | متخصصان پایداری زیست‌محیطی | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
+          <t>مهندسان کشاورزی | مدیران توسعه محصول و فناوری زیست‌سوخت | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | اقتصاددانان محیط زیست | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | مدیران و کارشناسان مدیریت مراتع | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان پایداری و توسعه پایدار | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>تحلیل تغییرات سامانه‌ها به‌منظور بهبود عملکرد زیست‌محیطی صنایع و پیشگیری از پیامدهای نامطلوب | به‌کارگیری یافته‌های مربوط به اکوسیستم‌های طبیعی در تحلیل سامانه‌های صنعتی و اقتصادی | اجرای ارزیابی‌های پایداری زیست‌محیطی با استفاده از روش‌های تحلیل جریان مواد و جریان ترکیبات | بازطراحی فرایندهای صنعتی خطی به چرخه‌های بسته و چرخشی جهت بازیافت و تبدیل ضایعات به مواد اولیه | مدل‌سازی پیچیده و پویای ریاضی برای تحلیل اثرات بوم‌شناختی و صنعتی | بررسی جریان محلی، منطقه‌ای و جهانی مواد و انرژی در فرآیندهای تولید صنعتی | شناسایی پیامدهای زیست‌محیطی کالاها، خدمات، طرح‌ها و پروژه‌های صنعتی | ارائه راهکارهای پایش و کاهش انتشار آلاینده‌ها و پسماندهای صنایع | تهیه گزارش‌های ارزیابی اثرات زیست‌محیطی EIA و ارائه به سازمان‌های ذی‌ربط و صنایع | ارائه مشاوره‌های فنی به مدیران صنایع در خصوص انطباق با الزامات و استانداردهای محیط زیست</t>
+          <t>تجزیه و تحلیل تغییرات طراحی‌شده برای بهبود عملکرد محیط‌زیستی سامانه‌های پیچیده و پرهیز از پیامدهای منفی ناخواسته. | به‌کارگیری پژوهش‌های جدید یا موجود درباره بوم‌سازگان‌های طبیعی برای درک سامانه‌های اقتصادی و صنعتی در بستر محیط‌زیست. | ساخت و نگهداری پایگاه‌های داده اطلاعات مربوط به گزینه‌های جایگزین انرژی، آلاینده‌ها، محیط‌های طبیعی، فرایندهای صنعتی و سایر اطلاعات مرتبط با تغییرات بوم‌شناختی. | انجام ارزیابی‌های محیط‌زیستی مطابق با استانداردها، مقررات یا قوانین مربوطه. | انجام تحلیل‌هایی برای تعیین بیشینه کاری که با مقدار معینی انرژی در یک سامانه انجام‌شدنی است، مانند سامانه‌های تولید صنعتی و سامانه‌های تصفیه پسماند. | انجام پژوهش کاربردی درباره آثار فرایندهای صنعتی بر حفاظت، احیا، سیاهه‌برداری، پایش یا بازمعرفی گونه‌ها به محیط طبیعی. | انجام ارزیابی‌های پایداری محیط‌زیستی، با استفاده از فنون تحلیل جریان مواد (MFA) یا تحلیل جریان ماده (SFA). | اجرای پروژه‌های علمی حفاظت، کاهش اثر یا احیا برای پیشگیری از آسیب به منابع، حفظ یکپارچگی زیستگاه‌های حساس و کمینه‌سازی اثر فعالیت‌های انسانی. | ساخت مدل‌های ریاضی پیچیده و پویا از جمعیت، اجتماع زیستی یا سامانه‌های بوم‌شناختی. | تدوین سناریوهای سرمایه‌گذاری در انرژی‌های جایگزین برای مقایسه هزینه‌ها و منافع اقتصادی و محیط‌زیستی. | تدوین یا آزمون پروتکل‌هایی برای پایش اجزای بوم‌سازگان و فرایندهای بوم‌شناختی. | ارزیابی اثربخشی برنامه‌های بوم‌شناسی صنعتی، با استفاده از تحلیل و کاربردهای آماری. | بررسی مصرف و جریان محلی، منطقه‌ای یا جهانی مواد و انرژی در فرایندهای تولید صنعتی. | بررسی مسائل اجتماعی و رابطه آن‌ها با سامانه‌های فنی و محیط‌زیست. | پیش‌بینی وضعیت یا شرایط آینده بوم‌سازگان‌ها، بر پایه تغییر شیوه‌های صنعتی یا شرایط محیط‌زیستی. | شناسایی اثرات محیط‌زیستی ناشی از محصولات، سامانه‌ها یا پروژه‌ها. | شناسایی یا مقایسه اجزای تشکیل‌دهنده یا روابط میان اجزای سامانه‌های صنعتی، اجتماعی و طبیعی. | شناسایی یا تدوین راهبردها یا روش‌هایی برای کمینه‌سازی اثر محیط‌زیستی فرایندهای تولید صنعتی. | شناسایی گزینه‌های پایدار جایگزین برای شیوه‌های صنعتی یا مدیریت پسماند. | بررسی حوادث اثرگذار بر محیط‌زیست برای ارزیابی پیامدهای بوم‌شناختی. | بررسی سازگاری گونه‌های مختلف جانوری و گیاهی با شرایط محیط‌زیستی تغییریافته. | بررسی اثر تغییر مدیریت یا کاربری اراضی بر بوم‌سازگان‌ها. | پایش اثر محیط‌زیستی فعالیت‌های توسعه، آلودگی یا تخریب اراضی. | انجام تحلیل‌هایی برای تعیین اینکه رفتار انسان چگونه بر تغییرات محیط‌زیست اثر می‌گذارد و از آن اثر می‌پذیرد. | انجام تحلیل‌های داده‌ستانده با گسترش محیط‌زیستی (EE I-O). | برنامه‌ریزی یا انجام پژوهش میدانی در موضوعاتی مانند تولید صنعتی، بوم‌شناسی صنعتی، بوم‌شناسی جمعیت و تولید یا پایداری محیط‌زیستی. | برنامه‌ریزی یا انجام مطالعاتی درباره پیامدهای بوم‌شناختی تغییرات تاریخی یا پیش‌بینی‌شده در فرایندهای صنعتی یا توسعه. | تهیه برنامه‌هایی برای مدیریت منابع تجدیدپذیر. | تهیه گزارش‌های فنی و پژوهشی، مانند گزارش‌های ارزیابی اثرات محیط‌زیستی، و انتقال نتایج به افراد فعال در صنعت، دولت یا عموم مردم. | ترویج استفاده از سامانه‌های مدیریت محیط‌زیست (EMS) برای کاهش پسماند یا بهبود استفاده محیط‌زیست‌سازگار از منابع طبیعی. | ارائه مواد فنی درباره مسائل محیط‌زیستی، دستورالعمل‌های نظارتی یا اقدامات انطباق به مدیران صنعتی. | پیشنهاد روش‌هایی برای حفاظت از محیط‌زیست یا کمینه‌سازی آسیب محیط‌زیستی ناشی از شیوه‌های تولید صنعتی. | بازطراحی سامانه‌های خطی یا حلقه‌باز به سامانه‌های چرخه‌ای یا حلقه‌بسته، به‌گونه‌ای که پسماندها به ورودی فرایندهای جدید تبدیل شوند و از بوم‌سازگان‌های طبیعی الگو بگیرند. | پژوهش درباره آثار محیط‌زیستی کاربری زمین و آب برای تعیین روش‌های بهبود شرایط محیط‌زیستی یا افزایش ستانده‌ها، مانند عملکرد محصولات کشاورزی. | پژوهش درباره منابع آلودگی برای تعیین اثر محیط‌زیستی یا تدوین روش‌های کاهش و کنترل آلودگی. | بازبینی شیوه‌های صنعتی، مانند روش‌ها و مواد به‌کاررفته در ساخت یا تولید، برای شناسایی مسئولیت‌های احتمالی و مخاطرات محیط‌زیستی. | بازبینی ادبیات پژوهشی برای به‌روز نگه‌داشتن دانش در موضوعات مرتبط با بوم‌شناسی صنعتی، مانند علوم فیزیکی، فناوری، اقتصاد و سیاست‌گذاری عمومی. | برگردان نظریه‌های بوم‌شناسی صنعتی به شیوه‌های اجرایی بوم‌صنعتی.</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | علوم پایه | سخن گفتن | شنیدن فعال | نگارش | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال استقرایی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری طبقه‌بندی | مرتب‌سازی اطلاعات | استدلال ریاضی | وضوح گفتار | دید نزدیک | تشخیص گفتار | روانی ایده‌ها | محاسبات عددی | انعطاف‌پذیری در نتیجه‌گیری | دید دور | ابتکار | توجه انتخابی | تجسم فضایی | سرعت ادراک</t>
+          <t>درک کتبی | استدلال استقرایی | درک شفاهی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | انعطاف‌پذیری دسته‌بندی | ترتیب‌دهی اطلاعات | استدلال ریاضی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | توانایی عددی | انعطاف‌پذیری بستار | بینایی دور | اصالت | توجه انتخابی | تجسم | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ستاره‌شناسان | دانشمندان علوم جوی و فضایی | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | دانشمندان داده | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست و بهداشت | دانشمندان و متخصصان محیط زیست و بهداشت | نقشه‌برداران ژئودزی | جغرافیدانان | تکنسین‌های زمین‌شناسی به استثنای آب‌شناسی | تکنسین‌های هیدرولوژی و آب‌شناسی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مهندسان معدن و زمین‌شناسی از جمله ایمنی معدن | مهندسان نفت | دانشمندان علوم خاک و گیاه‌شناسی | تکنسین‌های نقشه‌برداری | نقشه‌برداران | متخصصان منابع آب</t>
+          <t>ستاره‌شناسان و اخترشناسان | دانشمندان و کارشناسان علوم جوی و فضا | زیست‌شناسان | دانشمندان حفاظت از منابع طبیعی | دانشمندان داده | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان نقشه‌برداری ژئودزی | جغرافیدانان | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های آب‌شناسی و هیدرولوژی | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | مهندسان نفت | متخصصان خاک‌شناسی و علوم گیاهی | تکنسین‌های نقشه‌برداری و نقشه‌نگاری | مهندسان نقشه‌برداری | کارشناسان و متخصصان مدیریت منابع آب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>تحلیل و تفسیر داده‌های زمین‌شناسی، ژئوشیمیایی و ژئوفیزیکی حاصل از لاگ‌های چاه، مغزه‌گیری و تصاویر هوایی | برنامه‌ریزی و اجرای مطالعات میدانی، پیمایش‌های ژئوفیزیکی و عملیات حفاری اکتشافی | شناسایی و تخمین ذخایر احتمالی نفت، گاز، کانسارهای معدنی و مصالح ساختمانی | تهیه نقشه‌ها، مقاطع ساختاری، نمودارها و گزارش‌های تخصصی زمین‌شناسی | اندازه‌گیری ویژگی‌های زمین‌فیزیکی شامل گرانش و میدان‌های مغناطیسی با دستگاه‌های تخصصی | ارائه مشاوره در ساخت پروژه‌های عمرانی سدسازی، راه‌سازی، فونداسیون و پایدارسازی شیب‌ها | شناسایی و ارزیابی مخاطرات طبیعی نظیر رانش زمین، فرونشست، زلزله و فوران‌های آتشفشانی | آزمایش و آنالیز سنگ‌ها، کانی‌ها و خاک‌ها در آزمایشگاه به‌منظور تعیین ویژگی‌های پتروفیزیکی و کانی‌شناسی | بررسی وضعیت هیدروژئولوژی جهت مکان‌یابی دفن پسماند و بهسازی سایت‌های آلوده | ارائه توصیه‌های تخصصی پیرامون مکان‌یابی ایمن سازه‌های حساس و تاسیسات زیربنایی</t>
+          <t>ارائه مشاوره به شرکت‌های ساختمانی یا نهادهای دولتی درباره ساخت سد یا جاده، طراحی پی، کاربری زمین یا مدیریت منابع. | تجزیه و تحلیل و تفسیر داده‌های زمین‌شناسی، با استفاده از نرم‌افزارهای رایانه‌ای. | تجزیه و تحلیل و تفسیر اطلاعات زمین‌شناسی، ژئوشیمیایی یا ژئوفیزیکی از منابعی مانند داده‌های نقشه‌برداری، نگارهای چاه، گمانه‌ها یا عکس‌های هوایی. | ارزیابی حرکت آب‌های زیرزمینی یا سطحی برای ارائه مشاوره در موضوعاتی مانند مدیریت پسماند، انتخاب مسیر و محل، یا احیای محل‌های آلوده. | همکاری با پژوهشگران پزشکی یا سلامت برای رسیدگی به مشکلات سلامت مرتبط با مواد یا فرایندهای زمین‌شناختی. | انتقال یافته‌های زمین‌شناختی از راه نگارش مقالات پژوهشی، شرکت در همایش‌ها یا تدریس علوم زمین در دانشگاه‌ها. | انجام مطالعات زمین‌شناسی یا ژئوفیزیکی برای فراهم کردن اطلاعات مورد استفاده در توسعه منطقه‌ای، انتخاب محل یا اجرای پروژه‌های عمرانی. | طراحی نقشه‌های زمین‌شناسی معدن، پایش یکپارچگی سازه‌ای معدن، یا مشاوره و نظارت بر گروه‌های معدن‌کاری. | تعیین روش‌های وارد کردن ژئومتان یا هیدرات‌های متان به تولید جهانی انرژی یا ارزیابی پیامدهای محیط‌زیستی احتمالی این کار. | تعیین راه‌های کاهش پیامدهای منفی پراکنش گردوغبار معدنی. | توسعه نرم‌افزارهای کاربردی برای تجزیه و تحلیل و تفسیر داده‌های زمین‌شناسی. | تدوین راهبردهایی برای استخراج و احیای منابع با سازگاری بیشتر با محیط‌زیست. | تدوین روش‌هایی برای مهار یا استفاده از گازهایی که در فرایند تولید نفت به‌صورت پسماند سوزانده می‌شوند. | شناسایی ذخایر مصالح ساختمانی مناسب برای استفاده به‌عنوان سنگدانه بتن، خاکریز جاده یا سایر کاربردها. | شناسایی منابع جدید عناصر گروه پلاتین برای کاربردهای صنعتی، مانند پیل‌های سوختی خودرو یا سامانه‌های کاهش آلودگی. | شناسایی محل‌های ممکن برای پروژه‌های ترسیب کربن. | شناسایی مخاطرات بلایای طبیعی، مانند رانش زمین، زمین‌لرزه یا فوران آتشفشان. | بازرسی پروژه‌های ساختمانی برای تحلیل مسائل مهندسی، با استفاده از تجهیزات آزمون یا ماشین‌آلات حفاری. | بررسی ترکیب، ساختار یا تاریخچه پوسته زمین از راه گردآوری، بررسی، اندازه‌گیری یا طبقه‌بندی خاک‌ها، کانی‌ها، سنگ‌ها یا بقایای فسیلی. | مکان‌یابی و برآورد ذخایر احتمالی گاز طبیعی، نفت یا کانه‌های معدنی یا منابع آب زیرزمینی، با استفاده از عکس‌های هوایی، نمودارها یا نتایج پژوهش و نقشه‌برداری. | یافتن و بازبینی مقالات پژوهشی یا گزارش‌های محیط‌زیستی، تاریخی یا فنی. | مکان‌یابی منابع بالقوه انرژی زمین‌گرمایی. | اندازه‌گیری ویژگی‌های زمین، مانند گرانش یا میدان‌های مغناطیسی، با استفاده از تجهیزاتی مانند لرزه‌نگار، گرانی‌سنج، ترازوی پیچشی یا مغناطیس‌سنج. | برنامه‌ریزی یا انجام مطالعات و نقشه‌برداری‌های میدانی زمین‌شناسی، ژئوشیمیایی یا ژئوفیزیکی، نمونه‌برداری، یا برنامه‌های حفاری و آزمون که برای گردآوری داده‌های پژوهشی یا کاربردی به کار می‌روند. | تهیه نقشه‌های زمین‌شناسی، نمودارهای مقطعی، چارت‌ها یا گزارش‌های مربوط به استخراج مواد معدنی، کاربری زمین یا مدیریت منابع، با استفاده از نتایج کار میدانی یا پژوهش آزمایشگاهی. | ارائه مشاوره درباره مکان‌یابی ایمن پروژه‌های راکتور هسته‌ای جدید یا روش‌های مدیریت پسماند هسته‌ای. | پژوهش درباره فرایندهای ژئومکانیکی یا ژئوشیمیایی برای استفاده در پروژه‌های ترسیب کربن. | پژوهش درباره راه‌های کاهش ردپای بوم‌شناختی کلان‌شهرهایی که روزبه‌روز فراگیرتر می‌شوند. | بازبینی گزارش‌ها و انتشارات محیط‌زیستی، تاریخی یا فنی از نظر صحت. | بازبینی برنامه‌های کاری برای تعیین اثربخشی فعالیت‌های کاهش آلودگی خاک یا آب زیرزمینی. | مطالعه شاخص‌های تاریخی تغییر اقلیم موجود در مکان‌هایی مانند پوشش‌های یخی یا سازندهای سنگی برای تدوین مدل‌های تغییر اقلیم. | آزمون الماس‌ها یا ساینده‌های صنعتی، خاک یا سنگ برای تعیین ویژگی‌های زمین‌شناختی آن‌ها، با استفاده از ابزارهای نوری، پرتو ایکس، حرارتی، اسیدی یا دقیق.</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم پایه | درک مطلب | شنیدن فعال | سخن گفتن | ریاضیات | نگارش | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | علوم | درک مطلب | گوش دادن فعال | سخن گفتن | ریاضیات | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال ریاضی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری طبقه‌بندی | دید نزدیک | انعطاف‌پذیری در نتیجه‌گیری | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | ابتکار | محاسبات عددی | سرعت ادراک | دید دور | تجسم فضایی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال ریاضی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | روانی ایده‌ها | اصالت | توانایی عددی | سرعت ادراکی | بینایی دور | تجسم</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>دانشمندان علوم جوی و فضایی | زیست‌شناسان | متخصصان و مدیران احیای اراضی صنعتی متروکه | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | تکنسین‌ها و کاردان‌های فنی مهندسی محیط زیست | مهندسان محیط زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و حفاظت محیط زیست و بهداشت | دانشمندان و متخصصان محیط زیست و بهداشت | نقشه‌برداران ژئودزی | تکنسین‌های زمین‌شناسی به استثنای آب‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های هیدرولوژی و آب‌شناسی | بوم‌شناسان صنعتی | مهندسان معدن و زمین‌شناسی از جمله ایمنی معدن | مهندسان نفت | دانشمندان علوم خاک و گیاه‌شناسی | متخصصان منابع آب | مهندسان آب و فاضلاب</t>
+          <t>دانشمندان و کارشناسان علوم جوی و فضا | زیست‌شناسان | مدیران و کارشناسان احیا و بازسازی اراضی قهوه‌ای و آلوده | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | مهندسان نقشه‌برداری ژئودزی | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | تکنسین‌های آب‌شناسی و هیدرولوژی | بوم‌شناسان صنعتی | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | مهندسان نفت | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان و متخصصان مدیریت منابع آب | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>طراحی و اجرای مطالعات هیدروژئولوژیکی برای مدیریت بهینه و پایدار منابع آب سطحی و زیرزمینی | توسعه و پیاده‌سازی مدل‌های رقومی برای پیش‌بینی هیدرولوژیکی، سیلاب و بیلان آب | اندازه‌گیری، ثبت و تحلیل دبی جریان رودخانه‌ها، تراز آب‌های زیرزمینی و کیفیت منابع آب | نمونه‌برداری از منابع آب در مطالعات میدانی و سنجش داده‌های ایستگاه‌های پایش آنلاین | ارزیابی داده‌های هیدرولوژیکی به‌منظور امکان‌سنجی پروژه‌های سدسازی، شبکه‌های آبیاری و سامانه‌های هشدار سیل | مطالعه مخاطرات منابع آب شهری و روستایی شامل دوره‌های خشکسالی، طغیان سیلاب و افت تراز سفره‌ها | نصب، نگهداری و کالیبراسیون تجهیزات هیدرومتری، باران‌سنجی و رسوب‌سنجی | بررسی و حل اختلافات حقوقی و کارشناسی مربوط به حریم، بستر و برداشت از منابع آب عمومی | تهیه گزارش‌های تخصصی، اطلس‌های هیدرولوژی و نقشه‌های پهنه‌بندی حوضه‌های آبخیز | ارزیابی اثرات هیدروژئولوژیکی سایت‌های دفع پسماند و کانون‌های آلاینده بر آبخوان‌ها</t>
+          <t>اداره برنامه‌هایی که برای اطمینان از مسدودسازی صحیح چاه‌های متروکه طراحی شده‌اند. | پاسخ‌گویی به پرسش‌ها و ارائه کمک و اطلاعات فنی به پیمانکاران یا عموم مردم درباره موضوعاتی مانند حفر چاه، الزامات آیین‌نامه‌ای، آب‌شناسی و زمین‌شناسی. | به‌کارگیری یافته‌های پژوهشی برای کمک به کمینه‌سازی اثرات محیط‌زیستی آلودگی، بیماری‌های منتقله از آب، فرسایش و رسوب‌گذاری. | گردآوری و تجزیه و تحلیل نمونه‌های آب در چارچوب بررسی‌های میدانی یا برای اعتبارسنجی داده‌های پایشگرهای خودکار. | گردآوری و ارزیابی اطلاعات آب‌شناختی برای تهیه نقشه‌ها و چارت‌های ناوبری و پیش‌بینی شرایط جوی. | انجام پژوهش و انتقال اطلاعات برای ترویج حفاظت و صیانت از منابع آب. | انجام ارزیابی‌های اقلیمی کوتاه‌مدت و بلندمدت و مطالعه رخداد توفان‌ها. | هماهنگی و سرپرستی کار کارکنان متخصص و فنی، از جمله دستیاران پژوهشی، تکنولوژیست‌ها و تکنسین‌ها. | طراحی و انجام بررسی‌های علمی هیدروژئولوژیکی برای اطمینان از در دسترس بودن اطلاعات دقیق و مناسب جهت استفاده در تصمیم‌های مدیریت منابع آب. | طراحی سازه‌های عمرانی مرتبط با فعالیت‌های آب‌نگاری و سرپرستی ساخت، نصب و نگهداری آن‌ها. | تدوین مدل‌های رایانه‌ای برای پیش‌بینی‌های آب‌شناختی. | تدوین یا اصلاح روش‌های انجام مطالعات آب‌شناختی. | ارزیابی داده‌ها و ارائه توصیه درباره امکان‌پذیری پروژه‌های شهری، مانند نیروگاه‌های برق‌آبی، سامانه‌های آبیاری، سامانه‌های هشدار سیل و تأسیسات تصفیه پسماند. | ارزیابی داده‌های پژوهشی از نظر اثر آن‌ها بر موضوعاتی مانند حفاظت خاک و آب، برنامه‌ریزی مهار سیل و پیش‌بینی تأمین آب. | نصب، نگهداری و کالیبراسیون ابزارهایی مانند دستگاه‌های پایش تراز آب، بارش و رسوب. | بررسی شکایت‌ها یا اختلافات مرتبط با تغییر در آب‌های عمومی، شامل گردآوری اطلاعات، پیشنهاد گزینه‌های جایگزین، آگاه‌سازی طرف‌ها از پیشرفت کار و تهیه پیش‌نویس دستورها. | بررسی ویژگی‌ها، خاستگاه و رفتار یخچال‌های طبیعی، یخ، برف و خاک‌های همیشه‌یخ. | اندازه‌گیری و ترسیم نمودار پدیده‌هایی مانند تراز دریاچه‌ها، دبی رودخانه‌ها و تغییرات حجم آب. | پایش کار پیمانکاران حفر چاه، حفاران اکتشافی و مهندسان و اعمال مقررات مربوط به فعالیت آنان. | تهیه ارزیابی‌های هیدروژئولوژیکی محل‌های شناخته‌شده یا مظنون به پسماند خطرناک و تأسیسات تصفیه زمینی و دامداری‌های متمرکز. | تهیه گزارش‌های کتبی و شفاهی برای تشریح نتایج پژوهش، با استفاده از تصاویر، نقشه‌ها، پیوست‌ها و سایر اطلاعات. | بازبینی درخواست‌های طرح‌های مکانی و مجوزها و ارائه توصیه درباره تأیید، رد، اصلاح یا انجام بررسی بیشتر. | مطالعه و تجزیه و تحلیل جنبه‌های فیزیکی زمین از نظر مؤلفه‌های آب‌شناختی، شامل جو، آب‌کره و ساختار درونی. | مطالعه و مستندسازی مقدار، توزیع، وضعیت و توسعه آب‌های زیرزمینی و سطحی. | مطالعه مسائل تأمین آب عمومی، از جمله خطر سیل و خشک‌سالی، کیفیت آب، فاضلاب و اثرات آن بر زیستگاه‌های تالابی.</t>
         </is>
       </c>
     </row>
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم پایه | نظارت</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>فیزیک | شیمی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مهندسی و فناوری | آموزش و پرورش | جغرافیا | مدیریت و امور اداری</t>
+          <t>فیزیک | شیمی | ریاضیات | زبان انگلیسی | رایانه و الکترونیک | مهندسی و فناوری | آموزش و پرورش | جغرافیا | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | روانی ایده‌ها | ابتکار | توجه انتخابی | تقسیم توجه | تجسم فضایی | حفظ و یادآوری | استدلال ریاضی | محاسبات عددی | سرعت ادراک | انعطاف‌پذیری در نتیجه‌گیری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>شیمی‌دانان | دانشمندان علوم مواد | فیزیک‌دانان | ستاره‌شناسان | دانشمندان علوم جوی و فضایی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | دانشمندان و متخصصان محیط زیست و بهداشت | دانشمندان و فناوران سنجش از دور | بوم‌شناسان صنعتی | برنامه‌ریزان احیای محیط زیست | تحلیل‌گران خط‌مشی تغییر اقلیم | تکنسین‌های شیمی | تکنسین‌های هسته‌ای | تکنسین‌های زمین‌شناسی به استثنای آب‌شناسی | استادان شیمی دانشگاه | استادان فیزیک دانشگاه | مدیران علوم طبیعی | مهندسان مواد | مهندسان هسته‌ای</t>
+          <t>شیمی‌دانان | کارشناسان و دانشمندان علوم مواد | فیزیک‌دانان | ستاره‌شناسان و اخترشناسان | دانشمندان و کارشناسان علوم جوی و فضا | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | دانشمندان و فناوران سنجش از دور | بوم‌شناسان صنعتی | برنامه‌ریزان احیای محیط زیست | تحلیل‌گران خط‌مشی تغییر اقلیم | تکنسین‌های شیمی | تکنسین‌های هسته‌ای | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | استادان و مدرسان شیمی در دانشگاه‌ها و مراکز آموزش عالی | استادان و مدرسان فیزیک در دانشگاه‌ها و مراکز آموزش عالی | مدیران علوم طبیعی و پایه‌ای | مهندسان متالورژی و مواد | مهندسان هسته‌ای</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>انجام پژوهش‌های بنیادین و کاربردی در شاخه‌های تخصصی علوم فیزیکی | طراحی و اجرای آزمایش‌های تخصصی جهت بررسی پدیده‌های فیزیکی و شیمیایی | کار با تجهیزات و ابزارهای پیشرفته آزمایشگاهی برای سنجش فرآیندها و خواص فیزیکی | تدوین مدل‌های ریاضی و محاسباتی برای شبیه‌سازی سامانه‌های فیزیکی | تحلیل و اعتبارسنجی داده‌های تجربی و مشاهداتی و محاسبه عدم قطعیت در اندازه‌گیری‌ها | نگارش گزارش‌های فنی، مقالات علمی-پژوهشی و پروپوزال‌های دریافت اعتبار پژوهشی | کالیبراسیون، نگهداری و کنترل عملکرد ابزارهای دقیق آزمایشگاهی و میدانی | نظارت بر فعالیت تکنسین‌های آزمایشگاه و هماهنگی عملیات کارگاهی و صحرایی | حصول اطمینان از رعایت دقیق شیوه‌نامه‌های ایمنی در مواجهه با مواد خطرناک و پرتوها | مستندسازی و ثبت دقیق داده‌ها، روش‌ها، نتایج آزمون‌ها و فرآیندهای کالیبراسیون</t>
+          <t>انجام پژوهش در تخصص‌های علوم فیزیکی که جداگانه طبقه‌بندی نشده‌اند. | طراحی و انجام آزمایش برای بررسی پدیده‌های فیزیکی و شیمیایی. | کار با ابزارهای دقیق تخصصی برای اندازه‌گیری خواص و فرایندهای فیزیکی. | تدوین مدل‌های ریاضی و محاسباتی سامانه‌های فیزیکی. | تجزیه و تحلیل داده‌های آزمایشی و مشاهده‌ای و کمّی‌سازی عدم قطعیت اندازه‌گیری. | تهیه گزارش‌های پژوهشی، مقالات فنی و پیشنهادهای دریافت اعتبار مالی. | تفسیر یافته‌ها و ارائه مشاوره درباره کاربردهای صنعتی یا محیط‌زیستی آن‌ها. | کالیبراسیون و نگهداری تجهیزات علمی و راستی‌آزمایی عملکرد ابزارها. | گردآوری نمونه‌های میدانی و انجام اندازه‌گیری‌های محیط‌زیستی در شرایط گوناگون. | بازبینی ادبیات علمی و ارزیابی فنون اندازه‌گیری جدید. | سرپرستی تکنسین‌ها و هماهنگی عملیات آزمایشگاهی یا میدانی. | حصول اطمینان از رعایت رویه‌های ایمنی مربوط به مواد خطرناک و پرتوها. | ارائه یافته‌های فنی به مخاطبان علمی، نظارتی و مدیریتی. | نگهداری سوابق دقیق روش‌ها، کالیبراسیون‌ها و نتایج.</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | علوم پایه | شنیدن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>جغرافیا | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | فیزیک | طراحی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | زیست‌شناسی</t>
+          <t>جغرافیا | رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | فیزیک | طراحی | خدمات مشتری و شخصی | مدیریت و اداره | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | دید نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | مرتب‌سازی اطلاعات | استدلال ریاضی | انعطاف‌پذیری طبقه‌بندی | محاسبات عددی | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری در نتیجه‌گیری | تشخیص گفتار | ابتکار | تجسم فضایی | دید دور | توجه انتخابی | سرعت ادراک</t>
+          <t>استدلال استقرایی | استدلال قیاسی | حساسیت به مسئله | بینایی نزدیک | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | ترتیب‌دهی اطلاعات | استدلال ریاضی | انعطاف‌پذیری دسته‌بندی | توانایی عددی | وضوح گفتار | روانی ایده‌ها | انعطاف‌پذیری بستار | تشخیص گفتار | اصالت | تجسم | بینایی دور | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کاردان‌های فنی مهندسی و عملیات هوافضا | مهندسان هوافضا | دانشمندان علوم جوی و فضایی | تکنسین‌های اویونیک و الکترونیک هوانوردی | تکنسین‌های کالیبراسیون و ابزار دقیق | تصویربرداران تلویزیون، ویدئو و سینما | کارتوگراف‌ها و فتوگرامتریست‌ها | تکنسین‌ها و کاردان‌های فنی مهندسی برق و الکترونیک | تعمیرکاران تجهیزات الکترونیکی تجاری و صنعتی | تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک به استثنای رایانه | نقشه‌برداران ژئودزی | کارشناسان و تکنسین‌های سامانه‌های اطلاعات جغرافیایی GIS | تکنسین‌های زمین‌شناسی به استثنای آب‌شناسی | تکنسین‌های هیدرولوژی و آب‌شناسی | متخصصان سامانه‌های شناسایی با امواج رادیویی RFID | تکنسین‌های سنجش از دور | مهندسان رباتیک | تکنسین‌های رباتیک | تکنسین‌های نقشه‌برداری</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | دانشمندان و کارشناسان علوم جوی و فضا | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | تصویربرداران تلویزیون، ویدیو و سینما | کارشناسان نقشه‌نگاری و فتوگرامتری | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان نقشه‌برداری ژئودزی | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های آب‌شناسی و هیدرولوژی | متخصصان سامانه‌های شناسایی با امواج رادیویی | تکنسین‌های سنجش از دور | مهندسان رباتیک | تکنسین‌های رباتیک | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>تحلیل تصاویر و داده‌های ماهواره‌ای، پهپادی و هوایی با استفاده از نرم‌افزارهای تخصصی پردازش تصویر و GIS | به‌کارگیری تکنیک‌های سنجش از دور در مدل‌سازی منابع آب، پوشش اراضی و پدیده‌های زیست‌محیطی | پردازش داده‌های اپتیک، راداری و لیدار و تولید نقشه‌های کاربری اراضی و مدل‌های رقومی ارتفاعی | توسعه الگوریتم‌ها و اسکریپت‌های خودکار جهت تصحیحات رادیومتریک، اتمسفری و هندسی تصاویر | طراحی و پیاده‌سازی پایگاه‌های داده مکانی برای آرشیو و بازیابی داده‌های سنجش از دور | ادغام و تلفیق داده‌های سنجش از دور با سایر لایه‌های مکانی و آمارهای توصیفی | نظارت کیفی بر فرآیند اخذ و پردازش داده‌های سنجنده‌ها جهت حفظ صحت خروجی‌ها | هدایت و نظارت بر نصب، راه‌اندازی و آزمون نرم‌افزارها و سامانه‌های سخت‌افزاری سنجش از دور | پایش تغییرات جنگل‌ها، منابع زیست‌محیطی و ذخایر کربن با به‌کارگیری داده‌های سری زمانی ماهواره‌ای | تهیه گزارش‌های تحلیلی، نقشه‌های موضوعی و ارائه خروجی‌های فنی به کارفرمایان و مدیران</t>
+          <t>تجزیه و تحلیل داده‌های به‌دست‌آمده از هواپیما، ماهواره یا سکوهای زمینی، با استفاده از نرم‌افزارهای تحلیل آماری، نرم‌افزارهای تحلیل تصویر یا سامانه‌های اطلاعات جغرافیایی (GIS). | به‌کارگیری داده‌ها یا فنون سنجش از دور، مانند مدل‌سازی آب‌های سطحی یا تشخیص توده‌های گردوغبار، برای رسیدگی به مسائل محیط‌زیستی. | شرکت در نشست‌ها یا سمینارها یا مطالعه ادبیات روز برای به‌روز نگه‌داشتن دانش تحولات حوزه سنجش از دور. | گردآوری داده‌های پشتیبان، مانند داده‌های اقلیمی یا برداشت میدانی، برای تأیید تحلیل‌های داده سنجش از دور. | گردآوری و قالب‌بندی داده‌های تصویری برای افزایش کارایی آن‌ها. | انجام پژوهش درباره کاربرد یا ارتقای فناوری سنجش از دور. | طراحی یا اجرای راهبردهای گردآوری، تجزیه و تحلیل یا نمایش داده‌های جغرافیایی. | تدوین روال‌های خودکار برای تصحیح آثار اعوجاج‌زا در تصویر، مانند پوشش گیاهی سطح زمین. | توسعه فنون تحلیلی یا سامانه‌های حسگر جدید. | تدوین یا ساخت پایگاه‌های داده برای اطلاعات پروژه‌های سنجش از دور یا پروژه‌های مکانی مرتبط. | هدایت همه فعالیت‌های مرتبط با استقرار، بهره‌برداری یا ارتقای سخت‌افزار و نرم‌افزار سنجش از دور. | هدایت نصب یا آزمون سخت‌افزار یا نرم‌افزار جدید سنجش از دور. | بحث درباره اهداف پروژه، الزامات تجهیزاتی یا روش‌شناسی با همکاران یا اعضای تیم. | یکپارچه‌سازی سایر منابع داده مکانی در پروژه‌ها. | مدیریت یا تجزیه و تحلیل داده‌های به‌دست‌آمده از سامانه‌های سنجش از دور برای دستیابی به نتایج معنادار. | پایش کیفیت عملیات گردآوری داده سنجش از دور برای تعیین لزوم تغییر در رویه‌ها یا تجهیزات. | سازماندهی و نگهداری داده‌های مکانی و مستندات مرتبط با آن‌ها. | مشارکت در کار میدانی. | تهیه یا ارائه گزارش‌ها یا ارائه‌های اطلاعات پروژه‌های مکانی. | پردازش تصاویر هوایی یا ماهواره‌ای برای تولید محصولاتی مانند نقشه‌های پوشش زمین. | پیشنهاد تهیه سخت‌افزار یا نرم‌افزار جدید سنجش از دور. | راه‌اندازی یا نگهداری سامانه‌های گردآوری داده سنجش از دور. | آموزش تکنسین‌ها در زمینه استفاده از فناوری سنجش از دور. | استفاده از داده‌های سنجش از دور در فعالیت‌های پایش جنگل یا کربن برای ارزیابی اثر تغییرات محیط‌زیستی.</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | ریاضیات | تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال استقرایی | استدلال ریاضی | بیان کتبی | استدلال قیاسی | وضوح گفتار | درک شفاهی | بیان شفاهی | روانی ایده‌ها | حساسیت به مسئله | تشخیص گفتار | دید نزدیک | محاسبات عددی | مرتب‌سازی اطلاعات | ابتکار | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>درک کتبی | استدلال استقرایی | استدلال ریاضی | بیان کتبی | استدلال قیاسی | وضوح گفتار | درک شفاهی | بیان شفاهی | روانی ایده‌ها | حساسیت به مسئله | تشخیص گفتار | بینایی نزدیک | توانایی عددی | ترتیب‌دهی اطلاعات | اصالت | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>اکچوئری‌ها و محاسبان ریسک | تحلیل‌گران هوش تجاری | استادان علوم بازرگانی و تجارت دانشگاه | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان داده | استادان علوم اقتصادی دانشگاه | اقتصاددانان محیط زیست | تحلیل‌گران کمی مالی | متخصصان مدیریت ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | تحلیل‌گران تحقیق در عملیات | مشاوران مالی فردی | استادان علوم سیاسی دانشگاه | متخصصان علوم سیاسی | کارگزاران و نمایندگان فروش اوراق بهادار، کالاها و خدمات مالی | دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | آمارشناسان</t>
+          <t>اکچوئرها و کارشناسان محاسبات فنی بیمه | تحلیل‌گران هوش تجاری | استادان علوم اداری و مدیریت، آموزش عالی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان داده | استادان اقتصاد دانشگاه | اقتصاددانان محیط زیست | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | تحلیل‌گران مالی و سرمایه‌گذاری | مدیران صندوق‌های سرمایه‌گذاری | کارشناسان تحلیل تحقیقات بازار و بازاریابی | تحلیل‌گران تحقیق در عملیات | مشاوران مالی فردی | استادان علوم سیاسی دانشگاه | دانشمندان و پژوهشگران علوم سیاسی | کارشناسان فروش اوراق بهادار، کالاها و خدمات مالی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>گردآوری، پردازش و تحلیل داده‌های اقتصادی جهت تبیین روندهای بازار با به‌کارگیری مدل‌های ریاضی و اقتصادسنجی | تدوین گزارش‌های پژوهشی، مقالات علمی و متون سیاستی در زمینه‌های مختلف اقتصادی | تدوین استانداردها و شاخص‌های اقتصادی و ارزیابی پیش‌بینی‌ها جهت فرمول‌بندی خط‌مشی‌ها | پیش‌بینی الگوهای تولید، مصرف، تورم، نرخ اشتغال و تعادل در بازارهای کالا و سرمایه | ارائه راهکارها و پیشنهادهای سیاستی جهت بهبود عملکرد اقتصادی، مالیاتی و پولی کشور | بررسی پیامدهای اقتصادی و اجتماعی لوایح قانونی، طرح‌های مالیاتی و سیاست‌های تنظیمی دولت | ارائه خدمات مشاوره‌ای و تحلیل‌های اقتصادی به بخش‌های دولتی، بنگاه‌های خصوصی و سازمان‌ها | پیش‌بینی روند تقاضا و مصرف منابع تجدیدپذیر و ارزیابی بهره‌برداری از ذخایر تجدیدناپذیر | ارائه نظرات کارشناسی تخصصی در مراجع تصمیم‌گیری و کمیسیون‌های نظارتی و قانون‌گذاری | تدریس مبانی، نظریه‌ها و روش‌های اقتصادسنجی و تحلیل داده‌های اقتصادی</t>
+          <t>گردآوری، تجزیه و تحلیل و گزارش داده‌ها برای تبیین پدیده‌های اقتصادی و پیش‌بینی روندهای بازار، با به‌کارگیری مدل‌های ریاضی و فنون آماری. | انجام پژوهش درباره مسائل اقتصادی و انتشار یافته‌های پژوهشی از راه گزارش‌های فنی یا مقالات علمی در نشریات. | تدوین دستورالعمل‌ها و استانداردهای اقتصادی و تهیه دیدگاه‌های مورد استفاده در پیش‌بینی روندها و تدوین سیاست اقتصادی. | تبیین اثر اقتصادی سیاست‌ها برای عموم مردم. | پیش‌بینی تولید و مصرف منابع تجدیدپذیر و عرضه، مصرف و تحلیل‌رفتن منابع تجدیدناپذیر. | تدوین توصیه‌ها، سیاست‌ها یا برنامه‌هایی برای حل مسائل اقتصادی یا تفسیر بازارها. | ارائه مشاوره و خدمات مشورتی درباره روابط اقتصادی به کسب‌وکارها، نهادهای دولتی و خصوصی و سایر کارفرمایان. | ارائه پشتیبانی در دعاوی حقوقی، مانند نگارش گزارش برای شهادت کارشناسی یا حضور به‌عنوان شاهد کارشناس. | بازبینی اسناد نگاشته‌شده به‌دست دیگران. | مطالعه داده‌های اقتصادی و آماری در حوزه تخصصی، مانند مالیه، کار یا کشاورزی. | مطالعه پیامدهای اجتماعی‌اقتصادی سیاست‌های عمومی جدید، مانند لوایح پیشنهادی، مالیات‌ها، خدمات و مقررات. | سرپرستی پروژه‌های پژوهشی و پروژه‌های مطالعاتی دانشجویان. | تدریس نظریه‌ها، اصول و روش‌های اقتصاد. | ادای شهادت در جلسات استماع نظارتی یا قانون‌گذاری درباره آثار برآوردی تغییرات قانون یا سیاست عمومی و ارائه توصیه بر پایه تحلیل هزینه‌فایده.</t>
         </is>
       </c>
     </row>
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نگارش | شنیدن فعال | درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | سخن گفتن | نظارت | استراتژی‌های یادگیری</t>
+          <t>نگارش | گوش دادن فعال | درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | سخن گفتن | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>ریاضیات | اقتصاد و حسابداری | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | حقوق و مقررات دولتی</t>
+          <t>ریاضیات | اقتصاد و حسابداری | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش | قانون و دولت</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | استدلال ریاضی | درک شفاهی | بیان شفاهی | بیان کتبی | محاسبات عددی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | دید نزدیک | تشخیص گفتار | روانی ایده‌ها | ابتکار | مرتب‌سازی اطلاعات | انعطاف‌پذیری طبقه‌بندی | توجه انتخابی | انعطاف‌پذیری در نتیجه‌گیری | حفظ و یادآوری</t>
+          <t>درک کتبی | استدلال ریاضی | درک شفاهی | بیان شفاهی | بیان کتبی | توانایی عددی | وضوح گفتار | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | تشخیص گفتار | روانی ایده‌ها | اصالت | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | انعطاف‌پذیری بستار | حفظ کردن</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>زیست‌شناسان | مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | دانشمندان داده | استادان علوم اقتصادی دانشگاه | اقتصاددانان | برنامه‌ریزان احیای محیط زیست | دانشمندان و متخصصان محیط زیست و بهداشت | تحلیل‌گران کمی مالی | متخصصان مدیریت ریسک مالی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | متخصصان علوم سیاسی | جامعه‌شناسان | دانشمندان علوم خاک و گیاه‌شناسی | آمارشناسان | متخصصان پایداری زیست‌محیطی | جانورشناسان و زیست‌شناسان حیات وحش</t>
+          <t>زیست‌شناسان | مدیران ارشد پایداری سازمانی | تحلیل‌گران خط‌مشی تغییر اقلیم | دانشمندان حفاظت از منابع طبیعی | دانشمندان داده | استادان اقتصاد دانشگاه | اقتصاددانان | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | تحلیل‌گران کمّی مالی | کارشناسان ریسک مالی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | آب‌شناسان و هیدرولوژیست‌ها | بوم‌شناسان صنعتی | دانشمندان و پژوهشگران علوم سیاسی | جامعه‌شناسان | متخصصان خاک‌شناسی و علوم گیاهی | کارشناسان آمار | کارشناسان پایداری و توسعه پایدار | جانورشناسان و زیست‌شناسان حیات وحش</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>ارزیابی اقتصادی هزینه‌-فایده فعالیت‌ها، طرح‌ها و مقررات اثرگذار بر محیط زیست و ذخایر منابع طبیعی | ارزش‌گذاری اقتصادی خدمات اکوسیستمی، منابع آب، کیفیت هوا و تنوع زیستی | مدل‌سازی اقتصادسنجی برای پیش‌بینی پیامدهای اقتصادی سیاست‌های اقلیمی و زیست‌محیطی | مقایسه تطبیقی آثار اقتصادی و زیست‌محیطی راهکارهای جایگزین در تولید انرژی و مصرف منابع | طراحی مشوق‌ها، ابزارهای مالیاتی و سیاست‌های مالی جهت ترویج توسعه پایدار و کاهش انتشار آلاینده‌ها | تدوین گزارش‌های ارزیابی اثرات اقتصادی و اجتماعی خط‌مشی‌ها برای ارائه به مراجع تصمیم‌گیر | پژوهش در خصوص هزینه‌های بلندمدت تخریب و احیای محیط زیست و پیامدهای اتمام منابع تجدیدناپذیر | طراحی و تدوین پروپوزال‌های پژوهشی جهت اخذ اعتبارات تحقیقاتی از نهادهای ذی‌ربط | نگارش مقالات علمی، گزارش‌های سیاستی و بسته‌های تحلیلی در حوزه اقتصاد محیط زیست | ارائه راهکارهای اقتصادی با رویکرد ارتقای بهره‌وری سبز و پایداری در کسب‌وکارها</t>
+          <t>ارزیابی هزینه‌ها و منافع فعالیت‌ها، سیاست‌ها یا مقررات گوناگونی که بر محیط‌زیست یا ذخایر منابع طبیعی اثر می‌گذارند. | گردآوری و تجزیه و تحلیل داده‌ها برای مقایسه پیامدهای محیط‌زیستی گزینه‌های سیاستی یا اجرایی اقتصادی. | انجام پژوهش در موضوعات اقتصادی و محیط‌زیستی، مانند استفاده از سوخت‌های جایگزین، کاربری اراضی عمومی و خصوصی، حفاظت خاک، کنترل آلودگی هوا و آب، و حفاظت از گونه‌های در معرض خطر. | انجام پژوهش برای مطالعه روابط میان مسائل محیط‌زیستی و الگوهای تولید و مصرف اقتصادی. | نشان دادن یا ترویج منافع اقتصادی مقررات محیط‌زیستی درست. | تدوین مدل‌ها، پیش‌بینی‌ها یا سناریوهای اقتصادی برای پیش‌بینی پیامدهای اقتصادی و محیط‌زیستی آینده. | تدوین برنامه‌های پروژه‌های پژوهشی محیط‌زیستی، شامل اطلاعات بودجه، اهداف، خروجی‌ها، زمان‌بندی و الزامات منابع. | تدوین برنامه‌ها یا توصیه‌های سیاستی برای دستیابی به اهداف محیط‌زیستی به شیوه‌های مقرون‌به‌صرفه. | تدوین برنامه‌ها یا توصیه‌های سیاستی برای ترویج پایداری و توسعه پایدار. | تدوین سامانه‌هایی برای گردآوری، تجزیه و تحلیل و تفسیر داده‌های محیط‌زیستی و اقتصادی. | بررسی پایان‌پذیری منابع طبیعی یا هزینه‌های بلندمدت بازسازی محیط‌زیست. | شناسایی و پیشنهاد شیوه‌های کسب‌وکار سازگار با محیط‌زیست. | تفسیر شاخص‌ها برای تشخیص سلامت کلی یک محیط. | پایش یا تجزیه و تحلیل روندهای بازار و محیط‌زیست. | انجام مدل‌سازی ریاضی پیچیده، پویا و یکپارچه سامانه‌های بوم‌شناختی، محیط‌زیستی یا اقتصادی. | تهیه و ارائه ارائه‌هایی برای انتقال نتایج مطالعات اقتصادی و محیط‌زیستی، طرح توصیه‌های سیاستی یا افزایش آگاهی از پیامدهای محیط‌زیستی. | تدریس دروس اقتصاد محیط‌زیست. | نگارش پیشنهادهای پژوهشی و درخواست‌های اعطای اعتبار برای دریافت تأمین مالی خصوصی یا عمومی مطالعات محیط‌زیستی و اقتصادی. | نگارش بیانیه‌های اثر اجتماعی، حقوقی یا اقتصادی برای آگاهی‌بخشی به تصمیم‌گیران درباره سیاست‌ها، استانداردها یا برنامه‌های منابع طبیعی. | نگارش اسناد فنی یا مقالات علمی برای انتقال نتایج مطالعات یا پیش‌بینی‌های اقتصادی.</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | تفکر انتقادی | نگارش | شنیدن فعال | درک مطلب | ریاضیات | یادگیری فعال | استراتژی‌های یادگیری | نظارت</t>
+          <t>سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | درک مطلب | ریاضیات | یادگیری فعال | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | جامعه‌شناسی و مردم‌شناسی | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | روان‌شناسی | امور اداری و دفتری | ارتباطات و رسانه | آموزش و پرورش</t>
+          <t>زبان انگلیسی | جامعه‌شناسی و انسان‌شناسی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره | خدمات مشتری و شخصی | روان‌شناسی | اداری | ارتباطات و رسانه | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال ریاضی | دید نزدیک | وضوح گفتار | محاسبات عددی | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | حساسیت به مسئله | روانی ایده‌ها | انعطاف‌پذیری در نتیجه‌گیری | ابتکار | توجه انتخابی</t>
+          <t>استدلال استقرایی | بیان کتبی | درک کتبی | درک شفاهی | بیان شفاهی | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی | بینایی نزدیک | وضوح گفتار | توانایی عددی | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | حساسیت به مسئله | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توجه انتخابی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان آمار زیستی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | هماهنگ‌کنندگان پژوهش‌های بالینی | دانشمندان داده | مصاحبه‌گران واجدین شرایط برنامه‌های دولتی | تحلیل‌گران کمی مالی | نقشه‌برداران ژئودزی | تکنسین‌های اطلاعات سلامت و ثبت داده‌های پزشکی | روان‌شناسان صنعتی و سازمانی | هماهنگ‌کنندگان برنامه‌های آموزشی | تحلیل‌گران اطلاعاتی | مصاحبه‌گران به‌جز حوزه وام و اعتبارات | تحلیل‌گران مدیریت | تحلیل‌گران تحقیقات بازار و متخصصان بازاریابی | تحلیل‌گران تحقیق در عملیات | دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | دستیاران آماری | آمارشناسان</t>
+          <t>کارشناسان آمار زیستی | تحلیل‌گران هوش تجاری | مدیران داده‌های بالینی | هماهنگ‌کنندگان کارآزمایی‌های بالینی | دانشمندان داده | کارشناسان مصاحبه و احراز صلاحیت متقاضیان طرح‌های حمایتی و دولتی | تحلیل‌گران کمّی مالی | مهندسان نقشه‌برداری ژئودزی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | روان‌شناسان صنعتی و سازمانی | کارشناسان و هماهنگ‌کنندگان برنامه‌ریزی درسی و آموزشی | تحلیل‌گران داده‌ها و اطلاعات امنیتی | پرسشگران و مصاحبه‌گران، به جز امور وام و تعیین صلاحیت | کارشناسان تحلیل مدیریت و روش‌ها | کارشناسان تحلیل تحقیقات بازار و بازاریابی | تحلیل‌گران تحقیق در عملیات | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | جامعه‌شناسان | دستیاران و تکنسین‌های آمار | کارشناسان آمار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>طراحی پرسشنامه‌ها، شیوه‌نامه‌های مصاحبه و تعیین شاخص‌ها و ابزارهای گردآوری داده‌ها | تعیین روش‌های نمونه‌گیری، حجم نمونه و تدوین سازوکارهای وزن‌دهی آماری به داده‌ها | پردازش، پاک‌سازی و تحلیل آماری داده‌های حاصل از پیمایش‌ها و نظرسنجی‌ها با نرم‌افزارهای تخصصی | اجرای پیمایش‌ها از طریق مصاحبه‌های حضوری، پرسشنامه‌های برخط، گروه‌های کانون و نظرسنجی‌های تلفنی | نظارت بر عملکرد پرسشگران، مصاحبه‌گران و عوامل اجرایی جمع‌آوری اطلاعات و بازبینی خروجی‌ها | آموزش پرسشگران و تدوین شیوه‌نامه‌ها و راهنماهای اجرایی عملیات میدانی | پایش نرخ پاسخ‌گویی و تحلیل داده‌های مربوط به افت یا خطای پاسخ‌دهندگان | تهیه گزارش‌های تحلیلی، داشبوردها، جداول توصیفی و نمودارهای آماری از نتایج پیمایش‌ها | مستندسازی کامل متدولوژی، فرایند تدوین ابزارها و مراحل جمع‌آوری داده‌ها | تدوین پیشنهادهای پژوهشی و پروپوزال‌های تخصصی برای اجرای طرح‌های افکارسنجی و پیمایش بازار</t>
+          <t>تجزیه و تحلیل داده‌های حاصل از نظرسنجی‌ها، سوابق پیشین یا مطالعات موردی، با استفاده از نرم‌افزارهای آماری. | همکاری با سایر پژوهشگران در برنامه‌ریزی، اجرا و ارزیابی نظرسنجی‌ها. | انجام پژوهش برای گردآوری اطلاعات درباره موضوعات نظرسنجی. | اجرای نظرسنجی و گردآوری داده، با روش‌هایی مانند مصاحبه، پرسش‌نامه، گروه کانونی، نظرسنجی تحلیل بازار، نظرسنجی افکار عمومی، مرور ادبیات و بررسی پرونده‌ها. | رایزنی با کارفرمایان برای شناسایی نیازهای نظرسنجی و الزامات خاص، مانند نمونه‌های ویژه. | تعیین و تصریح جزئیات پروژه‌های نظرسنجی، شامل منابع اطلاعات، رویه‌های مورد استفاده و طراحی ابزارها و مواد نظرسنجی. | هدایت و بازبینی کار کارکنان، از جمله کارکنان پشتیبانی نظرسنجی و مصاحبه‌گرانی که داده‌ها را گردآوری می‌کنند. | هدایت به‌روزرسانی‌ها و تغییرات در اجرا و روش‌های نظرسنجی. | استخدام و آموزش جذب‌کنندگان و گردآورندگان داده. | پایش و ارزیابی پیشرفت و عملکرد نظرسنجی، با استفاده از گزارش‌های وضعیت نمونه و محاسبه نرخ پاسخ‌گویی. | تهیه و ارائه خلاصه‌ها و تحلیل‌های داده‌های نظرسنجی، شامل جدول‌ها، نمودارها و برگه‌های اطلاعاتی که فنون و نتایج نظرسنجی را تشریح می‌کنند. | تولید مستندات فرایند تدوین پرسش‌نامه، روش‌های گردآوری داده، طرح‌های نمونه‌گیری و تصمیم‌های مربوط به وزن‌دهی آماری نمونه. | بازبینی، طبقه‌بندی و ثبت داده‌های نظرسنجی برای آماده‌سازی تحلیل رایانه‌ای. | پشتیبانی، برنامه‌ریزی و هماهنگی عملیات یک یا چند نظرسنجی. | نگارش پیشنهادها برای کسب پروژه‌های جدید. | نگارش راهنماهای آموزشی برای استفاده مصاحبه‌گران نظرسنجی.</t>
         </is>
       </c>
     </row>
